--- a/Imoveis_Grupos.xlsx
+++ b/Imoveis_Grupos.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Imóveis" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grupos" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demandas" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Condomínios" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Imóveis" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Grupos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Demandas" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Condomínios" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Imóveis'!$A$1:$N$1</definedName>
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1122"/>
+  <dimension ref="A1:O1130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -56163,6 +56163,441 @@
         </is>
       </c>
       <c r="O1122" s="14" t="inlineStr"/>
+    </row>
+    <row r="1123">
+      <c r="A1123" s="14" t="inlineStr">
+        <is>
+          <t>29/06/2026, 14:30:17</t>
+        </is>
+      </c>
+      <c r="B1123" s="14" t="inlineStr">
+        <is>
+          <t>Corretores de sucesso 👏🇧🇷🎉🍾🙌🏡</t>
+        </is>
+      </c>
+      <c r="C1123" s="14" t="inlineStr">
+        <is>
+          <t>Mirna Ruas</t>
+        </is>
+      </c>
+      <c r="D1123" s="14" t="inlineStr"/>
+      <c r="E1123" s="14" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="F1123" s="14" t="inlineStr"/>
+      <c r="G1123" s="14" t="n"/>
+      <c r="H1123" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1123" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1123" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1123" s="14" t="n"/>
+      <c r="L1123" s="14" t="n"/>
+      <c r="M1123" s="14" t="inlineStr">
+        <is>
+          <t>Casa maravilhosa no jardim Munique
+✅  03 quartos
+✅  01 suíte 
+✅  02 banheiros
+✅  sala grande
+✅  cozinha
+✅  área gourmet 
+✅  churrasqueira 
+✅  piscina
+200 metros de terreno c/ 149 construção 
+Casa nova   
+Valor 750.000 aceita terreno de menor valor
+🛑Oportunidade para morar e investir! Bairro com alto</t>
+        </is>
+      </c>
+      <c r="N1123" s="14" t="inlineStr">
+        <is>
+          <t>Novo</t>
+        </is>
+      </c>
+      <c r="O1123" s="14" t="inlineStr"/>
+    </row>
+    <row r="1124">
+      <c r="A1124" s="14" t="inlineStr">
+        <is>
+          <t>29/06/2026, 14:33:19</t>
+        </is>
+      </c>
+      <c r="B1124" s="14" t="inlineStr">
+        <is>
+          <t>Maringá Apartamentos 🏘️</t>
+        </is>
+      </c>
+      <c r="C1124" s="14" t="inlineStr">
+        <is>
+          <t>Mariza Schmidt</t>
+        </is>
+      </c>
+      <c r="D1124" s="14" t="inlineStr"/>
+      <c r="E1124" s="14" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="F1124" s="14" t="inlineStr">
+        <is>
+          <t>Jardim Acimação</t>
+        </is>
+      </c>
+      <c r="G1124" s="14" t="n"/>
+      <c r="H1124" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1124" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1124" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1124" s="14" t="n"/>
+      <c r="L1124" s="14" t="n">
+        <v>550000</v>
+      </c>
+      <c r="M1124" s="14" t="inlineStr">
+        <is>
+          <t>Semi mobiliado, CRECI J10569, condomínio completo com piscina, academia, área infantil, salão de festas, launderia e sacada</t>
+        </is>
+      </c>
+      <c r="N1124" s="14" t="inlineStr">
+        <is>
+          <t>Novo</t>
+        </is>
+      </c>
+      <c r="O1124" s="14" t="inlineStr"/>
+    </row>
+    <row r="1125">
+      <c r="A1125" s="14" t="inlineStr">
+        <is>
+          <t>29/06/2026, 15:27:43</t>
+        </is>
+      </c>
+      <c r="B1125" s="14" t="inlineStr">
+        <is>
+          <t>Corretores de sucesso 👏🇧🇷🎉🍾🙌🏡</t>
+        </is>
+      </c>
+      <c r="C1125" s="14" t="inlineStr">
+        <is>
+          <t>Mirna Ruas</t>
+        </is>
+      </c>
+      <c r="D1125" s="14" t="inlineStr"/>
+      <c r="E1125" s="14" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="F1125" s="14" t="inlineStr">
+        <is>
+          <t>Parque das Laranjeiras</t>
+        </is>
+      </c>
+      <c r="G1125" s="14" t="n">
+        <v>400</v>
+      </c>
+      <c r="H1125" s="14" t="n"/>
+      <c r="I1125" s="14" t="n"/>
+      <c r="J1125" s="14" t="n"/>
+      <c r="K1125" s="14" t="n"/>
+      <c r="L1125" s="14" t="n">
+        <v>850000</v>
+      </c>
+      <c r="M1125" s="14" t="inlineStr">
+        <is>
+          <t>Área construída 167m². Espaçosa e arejada. Aceita terreno no mesmo bairro.</t>
+        </is>
+      </c>
+      <c r="N1125" s="14" t="inlineStr">
+        <is>
+          <t>Novo</t>
+        </is>
+      </c>
+      <c r="O1125" s="14" t="inlineStr"/>
+    </row>
+    <row r="1126">
+      <c r="A1126" s="14" t="inlineStr">
+        <is>
+          <t>29/06/2026, 16:10:23</t>
+        </is>
+      </c>
+      <c r="B1126" s="14" t="inlineStr">
+        <is>
+          <t>Imoveis Maringá e Região</t>
+        </is>
+      </c>
+      <c r="C1126" s="14" t="inlineStr">
+        <is>
+          <t>Alison Telles</t>
+        </is>
+      </c>
+      <c r="D1126" s="14" t="inlineStr"/>
+      <c r="E1126" s="14" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="F1126" s="14" t="inlineStr">
+        <is>
+          <t>Jardim Fregadoli</t>
+        </is>
+      </c>
+      <c r="G1126" s="14" t="n">
+        <v>116</v>
+      </c>
+      <c r="H1126" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1126" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1126" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1126" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1126" s="14" t="n">
+        <v>890000</v>
+      </c>
+      <c r="M1126" s="14" t="inlineStr">
+        <is>
+          <t>Casa à Venda – Jardim Fregadoli | Maringá/PR
+Imóvel moderno com acabamento de alto padrão, próximo à Avenida Gastão Vidigal e com fácil acesso a mercados, farmácias, restaurantes e demais comércios.
+São 116 m² de construção em um terreno de 170 m²,
+Jacuzzi com hidromassagem para 6 pessoas, além d</t>
+        </is>
+      </c>
+      <c r="N1126" s="14" t="inlineStr">
+        <is>
+          <t>Novo</t>
+        </is>
+      </c>
+      <c r="O1126" s="14" t="inlineStr"/>
+    </row>
+    <row r="1127">
+      <c r="A1127" s="14" t="inlineStr">
+        <is>
+          <t>29/06/2026, 16:10:50</t>
+        </is>
+      </c>
+      <c r="B1127" s="14" t="inlineStr">
+        <is>
+          <t>Corretores de sucesso 👏🇧🇷🎉🍾🙌🏡</t>
+        </is>
+      </c>
+      <c r="C1127" s="14" t="inlineStr">
+        <is>
+          <t>Alison Telles</t>
+        </is>
+      </c>
+      <c r="D1127" s="14" t="inlineStr"/>
+      <c r="E1127" s="14" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="F1127" s="14" t="inlineStr">
+        <is>
+          <t>Zona 08</t>
+        </is>
+      </c>
+      <c r="G1127" s="14" t="n">
+        <v>83</v>
+      </c>
+      <c r="H1127" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1127" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1127" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1127" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1127" s="14" t="n">
+        <v>950000</v>
+      </c>
+      <c r="M1127" s="14" t="inlineStr">
+        <is>
+          <t>*EDIFÍCIO MISANO RESIDENZA | ZONA 08 – MARINGÁ*
+Apartamento com 83 m² de área privativa, localizado próximo à Unicesumar e ao EuroGarden.
+• 1 suíte + 1 quarto
+• 2 banheiros
+• Sala de estar e jantar integradas
+• Sacada com churrasqueira a carvão
+• Screen Glass e rede de proteção
+• Sol da manhã
+• Ap</t>
+        </is>
+      </c>
+      <c r="N1127" s="14" t="inlineStr">
+        <is>
+          <t>Novo</t>
+        </is>
+      </c>
+      <c r="O1127" s="14" t="inlineStr"/>
+    </row>
+    <row r="1128">
+      <c r="A1128" s="14" t="inlineStr">
+        <is>
+          <t>29/06/2026, 16:37:30</t>
+        </is>
+      </c>
+      <c r="B1128" s="14" t="inlineStr">
+        <is>
+          <t>Imoveis Maringá e Região</t>
+        </is>
+      </c>
+      <c r="C1128" s="14" t="inlineStr">
+        <is>
+          <t>Odair</t>
+        </is>
+      </c>
+      <c r="D1128" s="14" t="inlineStr"/>
+      <c r="E1128" s="14" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="F1128" s="14" t="inlineStr"/>
+      <c r="G1128" s="14" t="n"/>
+      <c r="H1128" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1128" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1128" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1128" s="14" t="n"/>
+      <c r="L1128" s="14" t="n"/>
+      <c r="M1128" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ÓTIMA OPORTUNIDADE BOM JARDIM EM MARINGÁ ÁREA PRIVATIVA DE 138 METROS ÁREA DO LOTE 200 METROS.  *IMÓVEL COM.                *02 Quartos.                 *01suite Closet.             *02 BAnheiro social     *Sala Pe Direito Alto De 5 metros.      *Cozinha Com pia de Mármore De 2.70 mt e IIha.        </t>
+        </is>
+      </c>
+      <c r="N1128" s="14" t="inlineStr">
+        <is>
+          <t>Novo</t>
+        </is>
+      </c>
+      <c r="O1128" s="14" t="inlineStr"/>
+    </row>
+    <row r="1129">
+      <c r="A1129" s="14" t="inlineStr">
+        <is>
+          <t>29/06/2026, 17:16:17</t>
+        </is>
+      </c>
+      <c r="B1129" s="14" t="inlineStr">
+        <is>
+          <t>Corretores de sucesso 👏🇧🇷🎉🍾🙌🏡</t>
+        </is>
+      </c>
+      <c r="C1129" s="14" t="inlineStr">
+        <is>
+          <t>Edson Do Vale</t>
+        </is>
+      </c>
+      <c r="D1129" s="14" t="inlineStr"/>
+      <c r="E1129" s="14" t="inlineStr">
+        <is>
+          <t>Terreno</t>
+        </is>
+      </c>
+      <c r="F1129" s="14" t="inlineStr">
+        <is>
+          <t>Jardim Dias II</t>
+        </is>
+      </c>
+      <c r="G1129" s="14" t="n">
+        <v>413</v>
+      </c>
+      <c r="H1129" s="14" t="n"/>
+      <c r="I1129" s="14" t="n"/>
+      <c r="J1129" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1129" s="14" t="n"/>
+      <c r="L1129" s="14" t="n">
+        <v>350000</v>
+      </c>
+      <c r="M1129" s="14" t="inlineStr">
+        <is>
+          <t>Esquina das ruas Sebastião de Paula e Silva e Pietrobon. Próximo à Av Américo Belay e Av Morangueira. Dimensões aproximadas 20x20m. Estuda troca parcial por carro ou permuta por casa/apartamento até R$400.000</t>
+        </is>
+      </c>
+      <c r="N1129" s="14" t="inlineStr">
+        <is>
+          <t>Novo</t>
+        </is>
+      </c>
+      <c r="O1129" s="14" t="inlineStr"/>
+    </row>
+    <row r="1130">
+      <c r="A1130" s="14" t="inlineStr">
+        <is>
+          <t>29/06/2026, 17:24:02</t>
+        </is>
+      </c>
+      <c r="B1130" s="14" t="inlineStr">
+        <is>
+          <t>Corretores de sucesso 👏🇧🇷🎉🍾🙌🏡</t>
+        </is>
+      </c>
+      <c r="C1130" s="14" t="inlineStr">
+        <is>
+          <t>Edson Do Vale</t>
+        </is>
+      </c>
+      <c r="D1130" s="14" t="inlineStr"/>
+      <c r="E1130" s="14" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="F1130" s="14" t="inlineStr"/>
+      <c r="G1130" s="14" t="n"/>
+      <c r="H1130" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1130" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1130" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1130" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1130" s="14" t="n">
+        <v>822000</v>
+      </c>
+      <c r="M1130" s="14" t="inlineStr">
+        <is>
+          <t>Urban Yticon, 23º andar, 1 moto na garagem, closed, sacada, churrasqueira, sala, cozinha, lazer completo</t>
+        </is>
+      </c>
+      <c r="N1130" s="14" t="inlineStr">
+        <is>
+          <t>Novo</t>
+        </is>
+      </c>
+      <c r="O1130" s="14" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N1"/>
@@ -56635,7 +57070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57576,6 +58011,181 @@
       <c r="L37" s="14" t="n"/>
       <c r="M37" s="14" t="n"/>
       <c r="N37" s="14" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>29/06/2026, 15:53:39</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>Maringá Apartamentos 🏘️</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>João Brenner</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr"/>
+      <c r="E38" s="14" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="F38" s="14" t="inlineStr"/>
+      <c r="G38" s="14" t="n"/>
+      <c r="H38" s="14" t="n"/>
+      <c r="I38" s="14" t="n"/>
+      <c r="J38" s="14" t="n"/>
+      <c r="K38" s="14" t="n"/>
+      <c r="L38" s="14" t="n">
+        <v>800000</v>
+      </c>
+      <c r="M38" s="14" t="inlineStr">
+        <is>
+          <t>Pessoal,
+Alguém com um VISION pra venda, de preferência que pegue outro apartamento de menor valor , na faixa de R$800mil no negócio?
+Chama no privado.</t>
+        </is>
+      </c>
+      <c r="N38" s="14" t="inlineStr">
+        <is>
+          <t>Nova</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>29/06/2026, 16:18:48</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>BUSCA DE IMÓVEIS 🏡</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>Ludmilla Gargantini</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr"/>
+      <c r="E39" s="14" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="F39" s="14" t="inlineStr"/>
+      <c r="G39" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="H39" s="14" t="n"/>
+      <c r="I39" s="14" t="n"/>
+      <c r="J39" s="14" t="n"/>
+      <c r="K39" s="14" t="n"/>
+      <c r="L39" s="14" t="n"/>
+      <c r="M39" s="14" t="inlineStr">
+        <is>
+          <t>Pessoal
+Alguém com apartamento com acessibilidade de 100m² ??
+Enviar no PV por favor</t>
+        </is>
+      </c>
+      <c r="N39" s="14" t="inlineStr">
+        <is>
+          <t>Nova</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>29/06/2026, 16:19:30</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>Corretores de sucesso 👏🇧🇷🎉🍾🙌🏡</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>Denilson corretor</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr"/>
+      <c r="E40" s="14" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="inlineStr"/>
+      <c r="G40" s="14" t="n"/>
+      <c r="H40" s="14" t="n"/>
+      <c r="I40" s="14" t="n"/>
+      <c r="J40" s="14" t="n"/>
+      <c r="K40" s="14" t="n"/>
+      <c r="L40" s="14" t="n">
+        <v>480000</v>
+      </c>
+      <c r="M40" s="14" t="inlineStr">
+        <is>
+          <t>Cliente procura casa na regiao do Dias ate 480 mil Nova  
+Para visitar amanhã de manhã</t>
+        </is>
+      </c>
+      <c r="N40" s="14" t="inlineStr">
+        <is>
+          <t>Nova</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>29/06/2026, 16:28:22</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>Maringá Apartamentos 🏘️</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>Juliana Brenner Corretora de Imovéis</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="inlineStr"/>
+      <c r="E41" s="14" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="F41" s="14" t="inlineStr"/>
+      <c r="G41" s="14" t="n"/>
+      <c r="H41" s="14" t="n"/>
+      <c r="I41" s="14" t="n"/>
+      <c r="J41" s="14" t="n"/>
+      <c r="K41" s="14" t="n"/>
+      <c r="L41" s="14" t="n">
+        <v>750000</v>
+      </c>
+      <c r="M41" s="14" t="inlineStr">
+        <is>
+          <t>⚠️⚠️⚠️⚠️⚠️⚠️⚠️Procuro apartamento de *até R$ 750.000,00*, localizado nas Zonas 01, 03, 04, 07 ou 08.
+O imóvel *deve ser novo ou já reformado, com móveis planejados*. Pode estar alugado, pois a compra será para investimento.
+O proprietário *deve aceitar como parte do pagamento uma Toyota Hilux, com</t>
+        </is>
+      </c>
+      <c r="N41" s="14" t="inlineStr">
+        <is>
+          <t>Nova</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Imoveis_Grupos.xlsx
+++ b/Imoveis_Grupos.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Imóveis" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Grupos" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Demandas" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Condomínios" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Imóveis" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grupos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demandas" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Condomínios" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Imóveis'!$A$1:$N$1</definedName>
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1130"/>
+  <dimension ref="A1:O1134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -56598,6 +56598,237 @@
         </is>
       </c>
       <c r="O1130" s="14" t="inlineStr"/>
+    </row>
+    <row r="1131">
+      <c r="A1131" s="14" t="inlineStr">
+        <is>
+          <t>29/06/2026, 14:30:17</t>
+        </is>
+      </c>
+      <c r="B1131" s="14" t="inlineStr">
+        <is>
+          <t>Corretores de sucesso 👏🇧🇷🎉🍾🙌🏡</t>
+        </is>
+      </c>
+      <c r="C1131" s="14" t="inlineStr">
+        <is>
+          <t>Mirna Ruas</t>
+        </is>
+      </c>
+      <c r="D1131" s="14" t="inlineStr"/>
+      <c r="E1131" s="14" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="F1131" s="14" t="inlineStr"/>
+      <c r="G1131" s="14" t="n"/>
+      <c r="H1131" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1131" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1131" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1131" s="14" t="n"/>
+      <c r="L1131" s="14" t="n"/>
+      <c r="M1131" s="14" t="inlineStr">
+        <is>
+          <t>Casa maravilhosa no jardim Munique
+✅  03 quartos
+✅  01 suíte 
+✅  02 banheiros
+✅  sala grande
+✅  cozinha
+✅  área gourmet 
+✅  churrasqueira 
+✅  piscina
+200 metros de terreno c/ 149 construção 
+Casa nova   
+Valor 750.000 aceita terreno de menor valor
+🛑Oportunidade para morar e investir! Bairro com alto</t>
+        </is>
+      </c>
+      <c r="N1131" s="14" t="inlineStr">
+        <is>
+          <t>Novo</t>
+        </is>
+      </c>
+      <c r="O1131" s="14" t="inlineStr"/>
+    </row>
+    <row r="1132">
+      <c r="A1132" s="14" t="inlineStr">
+        <is>
+          <t>29/06/2026, 16:10:23</t>
+        </is>
+      </c>
+      <c r="B1132" s="14" t="inlineStr">
+        <is>
+          <t>Imoveis Maringá e Região</t>
+        </is>
+      </c>
+      <c r="C1132" s="14" t="inlineStr">
+        <is>
+          <t>Alison Telles</t>
+        </is>
+      </c>
+      <c r="D1132" s="14" t="inlineStr"/>
+      <c r="E1132" s="14" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="F1132" s="14" t="inlineStr">
+        <is>
+          <t>Jardim Fregadoli</t>
+        </is>
+      </c>
+      <c r="G1132" s="14" t="n">
+        <v>116</v>
+      </c>
+      <c r="H1132" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1132" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1132" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1132" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1132" s="14" t="n">
+        <v>890000</v>
+      </c>
+      <c r="M1132" s="14" t="inlineStr">
+        <is>
+          <t>Casa à Venda – Jardim Fregadoli | Maringá/PR
+Imóvel moderno com acabamento de alto padrão, próximo à Avenida Gastão Vidigal e com fácil acesso a mercados, farmácias, restaurantes e demais comércios.
+São 116 m² de construção em um terreno de 170 m²,
+Jacuzzi com hidromassagem para 6 pessoas, além d</t>
+        </is>
+      </c>
+      <c r="N1132" s="14" t="inlineStr">
+        <is>
+          <t>Novo</t>
+        </is>
+      </c>
+      <c r="O1132" s="14" t="inlineStr"/>
+    </row>
+    <row r="1133">
+      <c r="A1133" s="14" t="inlineStr">
+        <is>
+          <t>29/06/2026, 16:10:50</t>
+        </is>
+      </c>
+      <c r="B1133" s="14" t="inlineStr">
+        <is>
+          <t>Corretores de sucesso 👏🇧🇷🎉🍾🙌🏡</t>
+        </is>
+      </c>
+      <c r="C1133" s="14" t="inlineStr">
+        <is>
+          <t>Alison Telles</t>
+        </is>
+      </c>
+      <c r="D1133" s="14" t="inlineStr"/>
+      <c r="E1133" s="14" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="F1133" s="14" t="inlineStr">
+        <is>
+          <t>Zona 08</t>
+        </is>
+      </c>
+      <c r="G1133" s="14" t="n">
+        <v>83</v>
+      </c>
+      <c r="H1133" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1133" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1133" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1133" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1133" s="14" t="n">
+        <v>950000</v>
+      </c>
+      <c r="M1133" s="14" t="inlineStr">
+        <is>
+          <t>*EDIFÍCIO MISANO RESIDENZA | ZONA 08 – MARINGÁ*
+Apartamento com 83 m² de área privativa, localizado próximo à Unicesumar e ao EuroGarden.
+• 1 suíte + 1 quarto
+• 2 banheiros
+• Sala de estar e jantar integradas
+• Sacada com churrasqueira a carvão
+• Screen Glass e rede de proteção
+• Sol da manhã
+• Ap</t>
+        </is>
+      </c>
+      <c r="N1133" s="14" t="inlineStr">
+        <is>
+          <t>Novo</t>
+        </is>
+      </c>
+      <c r="O1133" s="14" t="inlineStr"/>
+    </row>
+    <row r="1134">
+      <c r="A1134" s="14" t="inlineStr">
+        <is>
+          <t>29/06/2026, 16:37:30</t>
+        </is>
+      </c>
+      <c r="B1134" s="14" t="inlineStr">
+        <is>
+          <t>Imoveis Maringá e Região</t>
+        </is>
+      </c>
+      <c r="C1134" s="14" t="inlineStr">
+        <is>
+          <t>Odair</t>
+        </is>
+      </c>
+      <c r="D1134" s="14" t="inlineStr"/>
+      <c r="E1134" s="14" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="F1134" s="14" t="inlineStr"/>
+      <c r="G1134" s="14" t="n"/>
+      <c r="H1134" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1134" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1134" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1134" s="14" t="n"/>
+      <c r="L1134" s="14" t="n"/>
+      <c r="M1134" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ÓTIMA OPORTUNIDADE BOM JARDIM EM MARINGÁ ÁREA PRIVATIVA DE 138 METROS ÁREA DO LOTE 200 METROS.  *IMÓVEL COM.                *02 Quartos.                 *01suite Closet.             *02 BAnheiro social     *Sala Pe Direito Alto De 5 metros.      *Cozinha Com pia de Mármore De 2.70 mt e IIha.        </t>
+        </is>
+      </c>
+      <c r="N1134" s="14" t="inlineStr">
+        <is>
+          <t>Novo</t>
+        </is>
+      </c>
+      <c r="O1134" s="14" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N1"/>
@@ -57070,7 +57301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:N45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58182,6 +58413,181 @@
         </is>
       </c>
       <c r="N41" s="14" t="inlineStr">
+        <is>
+          <t>Nova</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>29/06/2026, 15:53:39</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>Maringá Apartamentos 🏘️</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>João Brenner</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr"/>
+      <c r="E42" s="14" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="F42" s="14" t="inlineStr"/>
+      <c r="G42" s="14" t="n"/>
+      <c r="H42" s="14" t="n"/>
+      <c r="I42" s="14" t="n"/>
+      <c r="J42" s="14" t="n"/>
+      <c r="K42" s="14" t="n"/>
+      <c r="L42" s="14" t="n">
+        <v>800000</v>
+      </c>
+      <c r="M42" s="14" t="inlineStr">
+        <is>
+          <t>Pessoal,
+Alguém com um VISION pra venda, de preferência que pegue outro apartamento de menor valor , na faixa de R$800mil no negócio?
+Chama no privado.</t>
+        </is>
+      </c>
+      <c r="N42" s="14" t="inlineStr">
+        <is>
+          <t>Nova</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>29/06/2026, 16:18:48</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>BUSCA DE IMÓVEIS 🏡</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="inlineStr">
+        <is>
+          <t>Ludmilla Gargantini</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr"/>
+      <c r="E43" s="14" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="inlineStr"/>
+      <c r="G43" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="H43" s="14" t="n"/>
+      <c r="I43" s="14" t="n"/>
+      <c r="J43" s="14" t="n"/>
+      <c r="K43" s="14" t="n"/>
+      <c r="L43" s="14" t="n"/>
+      <c r="M43" s="14" t="inlineStr">
+        <is>
+          <t>Pessoal
+Alguém com apartamento com acessibilidade de 100m² ??
+Enviar no PV por favor</t>
+        </is>
+      </c>
+      <c r="N43" s="14" t="inlineStr">
+        <is>
+          <t>Nova</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>29/06/2026, 16:19:30</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>Corretores de sucesso 👏🇧🇷🎉🍾🙌🏡</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>Denilson corretor</t>
+        </is>
+      </c>
+      <c r="D44" s="14" t="inlineStr"/>
+      <c r="E44" s="14" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="F44" s="14" t="inlineStr"/>
+      <c r="G44" s="14" t="n"/>
+      <c r="H44" s="14" t="n"/>
+      <c r="I44" s="14" t="n"/>
+      <c r="J44" s="14" t="n"/>
+      <c r="K44" s="14" t="n"/>
+      <c r="L44" s="14" t="n">
+        <v>480000</v>
+      </c>
+      <c r="M44" s="14" t="inlineStr">
+        <is>
+          <t>Cliente procura casa na regiao do Dias ate 480 mil Nova  
+Para visitar amanhã de manhã</t>
+        </is>
+      </c>
+      <c r="N44" s="14" t="inlineStr">
+        <is>
+          <t>Nova</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>29/06/2026, 16:28:22</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>Maringá Apartamentos 🏘️</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>Juliana Brenner Corretora de Imovéis</t>
+        </is>
+      </c>
+      <c r="D45" s="14" t="inlineStr"/>
+      <c r="E45" s="14" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="F45" s="14" t="inlineStr"/>
+      <c r="G45" s="14" t="n"/>
+      <c r="H45" s="14" t="n"/>
+      <c r="I45" s="14" t="n"/>
+      <c r="J45" s="14" t="n"/>
+      <c r="K45" s="14" t="n"/>
+      <c r="L45" s="14" t="n">
+        <v>750000</v>
+      </c>
+      <c r="M45" s="14" t="inlineStr">
+        <is>
+          <t>⚠️⚠️⚠️⚠️⚠️⚠️⚠️Procuro apartamento de *até R$ 750.000,00*, localizado nas Zonas 01, 03, 04, 07 ou 08.
+O imóvel *deve ser novo ou já reformado, com móveis planejados*. Pode estar alugado, pois a compra será para investimento.
+O proprietário *deve aceitar como parte do pagamento uma Toyota Hilux, com</t>
+        </is>
+      </c>
+      <c r="N45" s="14" t="inlineStr">
         <is>
           <t>Nova</t>
         </is>

--- a/Imoveis_Grupos.xlsx
+++ b/Imoveis_Grupos.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1546"/>
+  <dimension ref="A1:O1570"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -35155,7 +35155,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1045" t="inlineStr"/>
       <c r="E1045" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -35210,7 +35209,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1046" t="inlineStr"/>
       <c r="E1046" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -35265,7 +35263,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1047" t="inlineStr"/>
       <c r="E1047" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -35320,7 +35317,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1048" t="inlineStr"/>
       <c r="E1048" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -35375,7 +35371,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1049" t="inlineStr"/>
       <c r="E1049" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -35424,7 +35419,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1050" t="inlineStr"/>
       <c r="E1050" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -35479,7 +35473,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1051" t="inlineStr"/>
       <c r="E1051" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -35531,7 +35524,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1052" t="inlineStr"/>
       <c r="E1052" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -35586,7 +35578,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1053" t="inlineStr"/>
       <c r="E1053" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -35641,7 +35632,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1054" t="inlineStr"/>
       <c r="E1054" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -35690,7 +35680,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1055" t="inlineStr"/>
       <c r="E1055" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -35745,7 +35734,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1056" t="inlineStr"/>
       <c r="E1056" t="inlineStr">
         <is>
           <t>Sobrado</t>
@@ -35800,7 +35788,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1057" t="inlineStr"/>
       <c r="E1057" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -35827,7 +35814,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1057" t="inlineStr"/>
     </row>
     <row r="1058">
       <c r="A1058" t="inlineStr">
@@ -35845,7 +35831,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1058" t="inlineStr"/>
       <c r="E1058" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -35894,7 +35879,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1059" t="inlineStr"/>
       <c r="E1059" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -35943,7 +35927,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1060" t="inlineStr"/>
       <c r="E1060" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -35998,7 +35981,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1061" t="inlineStr"/>
       <c r="E1061" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -36047,7 +36029,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1062" t="inlineStr"/>
       <c r="E1062" t="inlineStr">
         <is>
           <t>Imóvel Comercial</t>
@@ -36102,7 +36083,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1063" t="inlineStr"/>
       <c r="E1063" t="inlineStr">
         <is>
           <t>Ponto Comercial</t>
@@ -36151,7 +36131,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1064" t="inlineStr"/>
       <c r="E1064" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -36206,7 +36185,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1065" t="inlineStr"/>
       <c r="E1065" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -36233,7 +36211,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1065" t="inlineStr"/>
     </row>
     <row r="1066">
       <c r="A1066" t="inlineStr">
@@ -36251,7 +36228,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1066" t="inlineStr"/>
       <c r="E1066" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -36306,7 +36282,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1067" t="inlineStr"/>
       <c r="E1067" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -36355,7 +36330,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1068" t="inlineStr"/>
       <c r="E1068" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -36388,7 +36362,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1068" t="inlineStr"/>
     </row>
     <row r="1069">
       <c r="A1069" t="inlineStr">
@@ -36406,7 +36379,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1069" t="inlineStr"/>
       <c r="E1069" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -36455,7 +36427,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1070" t="inlineStr"/>
       <c r="E1070" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -36510,7 +36481,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1071" t="inlineStr"/>
       <c r="E1071" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -36537,7 +36507,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1071" t="inlineStr"/>
     </row>
     <row r="1072">
       <c r="A1072" t="inlineStr">
@@ -36555,7 +36524,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1072" t="inlineStr"/>
       <c r="E1072" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -36610,7 +36578,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1073" t="inlineStr"/>
       <c r="E1073" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -36637,7 +36604,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1073" t="inlineStr"/>
     </row>
     <row r="1074">
       <c r="A1074" t="inlineStr">
@@ -36655,7 +36621,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1074" t="inlineStr"/>
       <c r="E1074" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -36704,7 +36669,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1075" t="inlineStr"/>
       <c r="E1075" t="inlineStr">
         <is>
           <t>Prédio Comercial</t>
@@ -36737,7 +36701,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1075" t="inlineStr"/>
     </row>
     <row r="1076">
       <c r="A1076" t="inlineStr">
@@ -36755,7 +36718,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1076" t="inlineStr"/>
       <c r="E1076" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -36782,7 +36744,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1076" t="inlineStr"/>
     </row>
     <row r="1077">
       <c r="A1077" t="inlineStr">
@@ -36800,7 +36761,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1077" t="inlineStr"/>
       <c r="E1077" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -36833,7 +36793,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1077" t="inlineStr"/>
     </row>
     <row r="1078">
       <c r="A1078" t="inlineStr">
@@ -36851,7 +36810,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1078" t="inlineStr"/>
       <c r="E1078" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -36878,7 +36836,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1078" t="inlineStr"/>
     </row>
     <row r="1079">
       <c r="A1079" t="inlineStr">
@@ -36896,7 +36853,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1079" t="inlineStr"/>
       <c r="E1079" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -36923,7 +36879,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1079" t="inlineStr"/>
     </row>
     <row r="1080">
       <c r="A1080" t="inlineStr">
@@ -36941,7 +36896,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1080" t="inlineStr"/>
       <c r="E1080" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -36974,7 +36928,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1080" t="inlineStr"/>
     </row>
     <row r="1081">
       <c r="A1081" t="inlineStr">
@@ -36992,7 +36945,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1081" t="inlineStr"/>
       <c r="E1081" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -37025,7 +36977,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1081" t="inlineStr"/>
     </row>
     <row r="1082">
       <c r="A1082" t="inlineStr">
@@ -37043,7 +36994,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1082" t="inlineStr"/>
       <c r="E1082" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -37076,7 +37026,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1082" t="inlineStr"/>
     </row>
     <row r="1083">
       <c r="A1083" t="inlineStr">
@@ -37094,7 +37043,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1083" t="inlineStr"/>
       <c r="E1083" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -37143,7 +37091,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1084" t="inlineStr"/>
       <c r="E1084" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -37170,7 +37117,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1084" t="inlineStr"/>
     </row>
     <row r="1085">
       <c r="A1085" t="inlineStr">
@@ -37188,7 +37134,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1085" t="inlineStr"/>
       <c r="E1085" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -37215,7 +37160,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1085" t="inlineStr"/>
     </row>
     <row r="1086">
       <c r="A1086" t="inlineStr">
@@ -37233,7 +37177,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1086" t="inlineStr"/>
       <c r="E1086" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -37260,7 +37203,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1086" t="inlineStr"/>
     </row>
     <row r="1087">
       <c r="A1087" t="inlineStr">
@@ -37278,7 +37220,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1087" t="inlineStr"/>
       <c r="E1087" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -37333,7 +37274,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1088" t="inlineStr"/>
       <c r="E1088" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -37366,7 +37306,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1088" t="inlineStr"/>
     </row>
     <row r="1089">
       <c r="A1089" t="inlineStr">
@@ -37384,7 +37323,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1089" t="inlineStr"/>
       <c r="E1089" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -37433,7 +37371,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1090" t="inlineStr"/>
       <c r="E1090" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -37460,7 +37397,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1090" t="inlineStr"/>
     </row>
     <row r="1091">
       <c r="A1091" t="inlineStr">
@@ -37478,7 +37414,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1091" t="inlineStr"/>
       <c r="E1091" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -37505,7 +37440,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1091" t="inlineStr"/>
     </row>
     <row r="1092">
       <c r="A1092" t="inlineStr">
@@ -37523,7 +37457,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1092" t="inlineStr"/>
       <c r="E1092" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -37572,7 +37505,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1093" t="inlineStr"/>
       <c r="E1093" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -37599,7 +37531,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1093" t="inlineStr"/>
     </row>
     <row r="1094">
       <c r="A1094" t="inlineStr">
@@ -37617,7 +37548,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1094" t="inlineStr"/>
       <c r="E1094" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -37644,7 +37574,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1094" t="inlineStr"/>
     </row>
     <row r="1095">
       <c r="A1095" t="inlineStr">
@@ -37662,7 +37591,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1095" t="inlineStr"/>
       <c r="E1095" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -37695,7 +37623,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1095" t="inlineStr"/>
     </row>
     <row r="1096">
       <c r="A1096" t="inlineStr">
@@ -37713,7 +37640,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1096" t="inlineStr"/>
       <c r="E1096" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -37746,7 +37672,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1096" t="inlineStr"/>
     </row>
     <row r="1097">
       <c r="A1097" t="inlineStr">
@@ -37764,7 +37689,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1097" t="inlineStr"/>
       <c r="E1097" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -37797,7 +37721,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1097" t="inlineStr"/>
     </row>
     <row r="1098">
       <c r="A1098" t="inlineStr">
@@ -37815,7 +37738,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1098" t="inlineStr"/>
       <c r="E1098" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -37870,7 +37792,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1099" t="inlineStr"/>
       <c r="E1099" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -37897,7 +37818,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1099" t="inlineStr"/>
     </row>
     <row r="1100">
       <c r="A1100" t="inlineStr">
@@ -37915,7 +37835,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1100" t="inlineStr"/>
       <c r="E1100" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -37948,7 +37867,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1100" t="inlineStr"/>
     </row>
     <row r="1101">
       <c r="A1101" t="inlineStr">
@@ -37966,7 +37884,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1101" t="inlineStr"/>
       <c r="E1101" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -37993,7 +37910,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1101" t="inlineStr"/>
     </row>
     <row r="1102">
       <c r="A1102" t="inlineStr">
@@ -38011,7 +37927,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1102" t="inlineStr"/>
       <c r="E1102" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -38044,7 +37959,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1102" t="inlineStr"/>
     </row>
     <row r="1103">
       <c r="A1103" t="inlineStr">
@@ -38062,7 +37976,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1103" t="inlineStr"/>
       <c r="E1103" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -38092,7 +38005,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1103" t="inlineStr"/>
     </row>
     <row r="1104">
       <c r="A1104" t="inlineStr">
@@ -38110,7 +38022,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1104" t="inlineStr"/>
       <c r="E1104" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -38143,7 +38054,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1104" t="inlineStr"/>
     </row>
     <row r="1105">
       <c r="A1105" t="inlineStr">
@@ -38161,7 +38071,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1105" t="inlineStr"/>
       <c r="E1105" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -38194,7 +38103,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1105" t="inlineStr"/>
     </row>
     <row r="1106">
       <c r="A1106" t="inlineStr">
@@ -38212,7 +38120,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1106" t="inlineStr"/>
       <c r="E1106" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -38242,7 +38149,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1106" t="inlineStr"/>
     </row>
     <row r="1107">
       <c r="A1107" t="inlineStr">
@@ -38260,7 +38166,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1107" t="inlineStr"/>
       <c r="E1107" t="inlineStr">
         <is>
           <t>Sobrado</t>
@@ -38312,7 +38217,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1108" t="inlineStr"/>
       <c r="E1108" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -38339,7 +38243,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1108" t="inlineStr"/>
     </row>
     <row r="1109">
       <c r="A1109" t="inlineStr">
@@ -38357,7 +38260,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1109" t="inlineStr"/>
       <c r="E1109" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -38390,7 +38292,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1109" t="inlineStr"/>
     </row>
     <row r="1110">
       <c r="A1110" t="inlineStr">
@@ -38408,7 +38309,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1110" t="inlineStr"/>
       <c r="E1110" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -38441,7 +38341,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1110" t="inlineStr"/>
     </row>
     <row r="1111">
       <c r="A1111" t="inlineStr">
@@ -38459,7 +38358,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1111" t="inlineStr"/>
       <c r="E1111" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -38492,7 +38390,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1111" t="inlineStr"/>
     </row>
     <row r="1112">
       <c r="A1112" t="inlineStr">
@@ -38510,7 +38407,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1112" t="inlineStr"/>
       <c r="E1112" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -38559,7 +38455,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1113" t="inlineStr"/>
       <c r="E1113" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -38592,7 +38487,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1113" t="inlineStr"/>
     </row>
     <row r="1114">
       <c r="A1114" t="inlineStr">
@@ -38610,7 +38504,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1114" t="inlineStr"/>
       <c r="E1114" t="inlineStr">
         <is>
           <t>Sobrado</t>
@@ -38643,7 +38536,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1114" t="inlineStr"/>
     </row>
     <row r="1115">
       <c r="A1115" t="inlineStr">
@@ -38661,7 +38553,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1115" t="inlineStr"/>
       <c r="E1115" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -38694,7 +38585,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1115" t="inlineStr"/>
     </row>
     <row r="1116">
       <c r="A1116" t="inlineStr">
@@ -38712,7 +38602,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1116" t="inlineStr"/>
       <c r="E1116" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -38767,7 +38656,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1117" t="inlineStr"/>
       <c r="E1117" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -38797,7 +38685,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1117" t="inlineStr"/>
     </row>
     <row r="1118">
       <c r="A1118" t="inlineStr">
@@ -38815,7 +38702,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1118" t="inlineStr"/>
       <c r="E1118" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -38848,7 +38734,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1118" t="inlineStr"/>
     </row>
     <row r="1119">
       <c r="A1119" t="inlineStr">
@@ -38866,7 +38751,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1119" t="inlineStr"/>
       <c r="E1119" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -38893,7 +38777,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1119" t="inlineStr"/>
     </row>
     <row r="1120">
       <c r="A1120" t="inlineStr">
@@ -38911,7 +38794,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1120" t="inlineStr"/>
       <c r="E1120" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -38944,7 +38826,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1120" t="inlineStr"/>
     </row>
     <row r="1121">
       <c r="A1121" t="inlineStr">
@@ -38962,7 +38843,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1121" t="inlineStr"/>
       <c r="E1121" t="inlineStr">
         <is>
           <t>Prédio Comercial</t>
@@ -38995,7 +38875,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1121" t="inlineStr"/>
     </row>
     <row r="1122">
       <c r="A1122" t="inlineStr">
@@ -39013,7 +38892,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1122" t="inlineStr"/>
       <c r="E1122" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -39040,7 +38918,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1122" t="inlineStr"/>
     </row>
     <row r="1123">
       <c r="A1123" t="inlineStr">
@@ -39058,7 +38935,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1123" t="inlineStr"/>
       <c r="E1123" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -39091,7 +38967,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1123" t="inlineStr"/>
     </row>
     <row r="1124">
       <c r="A1124" t="inlineStr">
@@ -39109,7 +38984,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1124" t="inlineStr"/>
       <c r="E1124" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -39136,7 +39010,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1124" t="inlineStr"/>
     </row>
     <row r="1125">
       <c r="A1125" t="inlineStr">
@@ -39154,7 +39027,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1125" t="inlineStr"/>
       <c r="E1125" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -39181,7 +39053,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1125" t="inlineStr"/>
     </row>
     <row r="1126">
       <c r="A1126" t="inlineStr">
@@ -39199,7 +39070,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1126" t="inlineStr"/>
       <c r="E1126" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -39226,7 +39096,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1126" t="inlineStr"/>
     </row>
     <row r="1127">
       <c r="A1127" t="inlineStr">
@@ -39244,7 +39113,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1127" t="inlineStr"/>
       <c r="E1127" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -39271,7 +39139,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1127" t="inlineStr"/>
     </row>
     <row r="1128">
       <c r="A1128" t="inlineStr">
@@ -39289,7 +39156,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1128" t="inlineStr"/>
       <c r="E1128" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -39322,7 +39188,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1128" t="inlineStr"/>
     </row>
     <row r="1129">
       <c r="A1129" t="inlineStr">
@@ -39340,7 +39205,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1129" t="inlineStr"/>
       <c r="E1129" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -39367,7 +39231,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1129" t="inlineStr"/>
     </row>
     <row r="1130">
       <c r="A1130" t="inlineStr">
@@ -39385,7 +39248,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1130" t="inlineStr"/>
       <c r="E1130" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -39412,7 +39274,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1130" t="inlineStr"/>
     </row>
     <row r="1131">
       <c r="A1131" t="inlineStr">
@@ -39430,7 +39291,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1131" t="inlineStr"/>
       <c r="E1131" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -39457,7 +39317,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1131" t="inlineStr"/>
     </row>
     <row r="1132">
       <c r="A1132" t="inlineStr">
@@ -39475,7 +39334,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1132" t="inlineStr"/>
       <c r="E1132" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -39502,7 +39360,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1132" t="inlineStr"/>
     </row>
     <row r="1133">
       <c r="A1133" t="inlineStr">
@@ -39520,7 +39377,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1133" t="inlineStr"/>
       <c r="E1133" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -39547,7 +39403,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1133" t="inlineStr"/>
     </row>
     <row r="1134">
       <c r="A1134" t="inlineStr">
@@ -39565,7 +39420,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1134" t="inlineStr"/>
       <c r="E1134" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -39592,7 +39446,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1134" t="inlineStr"/>
     </row>
     <row r="1135">
       <c r="A1135" t="inlineStr">
@@ -39610,7 +39463,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1135" t="inlineStr"/>
       <c r="E1135" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -39637,7 +39489,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1135" t="inlineStr"/>
     </row>
     <row r="1136">
       <c r="A1136" t="inlineStr">
@@ -39655,7 +39506,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1136" t="inlineStr"/>
       <c r="E1136" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -39688,7 +39538,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1136" t="inlineStr"/>
     </row>
     <row r="1137">
       <c r="A1137" t="inlineStr">
@@ -39706,7 +39555,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1137" t="inlineStr"/>
       <c r="E1137" t="inlineStr">
         <is>
           <t>Imóvel Comercial</t>
@@ -39736,7 +39584,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1137" t="inlineStr"/>
     </row>
     <row r="1138">
       <c r="A1138" t="inlineStr">
@@ -39754,7 +39601,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1138" t="inlineStr"/>
       <c r="E1138" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -39781,7 +39627,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1138" t="inlineStr"/>
     </row>
     <row r="1139">
       <c r="A1139" t="inlineStr">
@@ -39799,7 +39644,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1139" t="inlineStr"/>
       <c r="E1139" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -39832,7 +39676,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1139" t="inlineStr"/>
     </row>
     <row r="1140">
       <c r="A1140" t="inlineStr">
@@ -39850,7 +39693,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1140" t="inlineStr"/>
       <c r="E1140" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -39877,7 +39719,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1140" t="inlineStr"/>
     </row>
     <row r="1141">
       <c r="A1141" t="inlineStr">
@@ -39895,7 +39736,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1141" t="inlineStr"/>
       <c r="E1141" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -39922,7 +39762,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1141" t="inlineStr"/>
     </row>
     <row r="1142">
       <c r="A1142" t="inlineStr">
@@ -39940,7 +39779,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1142" t="inlineStr"/>
       <c r="E1142" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -39967,7 +39805,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1142" t="inlineStr"/>
     </row>
     <row r="1143">
       <c r="A1143" t="inlineStr">
@@ -39985,7 +39822,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1143" t="inlineStr"/>
       <c r="E1143" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -40012,7 +39848,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1143" t="inlineStr"/>
     </row>
     <row r="1144">
       <c r="A1144" t="inlineStr">
@@ -40030,7 +39865,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1144" t="inlineStr"/>
       <c r="E1144" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -40057,7 +39891,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1144" t="inlineStr"/>
     </row>
     <row r="1145">
       <c r="A1145" t="inlineStr">
@@ -40075,7 +39908,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1145" t="inlineStr"/>
       <c r="E1145" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -40108,7 +39940,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1145" t="inlineStr"/>
     </row>
     <row r="1146">
       <c r="A1146" t="inlineStr">
@@ -40126,7 +39957,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1146" t="inlineStr"/>
       <c r="E1146" t="inlineStr">
         <is>
           <t>Sala Comercial</t>
@@ -40156,7 +39986,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1146" t="inlineStr"/>
     </row>
     <row r="1147">
       <c r="A1147" t="inlineStr">
@@ -40174,7 +40003,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1147" t="inlineStr"/>
       <c r="E1147" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -40207,7 +40035,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1147" t="inlineStr"/>
     </row>
     <row r="1148">
       <c r="A1148" t="inlineStr">
@@ -40225,7 +40052,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1148" t="inlineStr"/>
       <c r="E1148" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -40252,7 +40078,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1148" t="inlineStr"/>
     </row>
     <row r="1149">
       <c r="A1149" t="inlineStr">
@@ -40270,7 +40095,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1149" t="inlineStr"/>
       <c r="E1149" t="inlineStr">
         <is>
           <t>Sala Comercial</t>
@@ -40319,7 +40143,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1150" t="inlineStr"/>
       <c r="E1150" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -40352,7 +40175,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1150" t="inlineStr"/>
     </row>
     <row r="1151">
       <c r="A1151" t="inlineStr">
@@ -40370,7 +40192,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1151" t="inlineStr"/>
       <c r="E1151" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -40397,7 +40218,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1151" t="inlineStr"/>
     </row>
     <row r="1152">
       <c r="A1152" t="inlineStr">
@@ -40415,7 +40235,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1152" t="inlineStr"/>
       <c r="E1152" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -40442,7 +40261,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1152" t="inlineStr"/>
     </row>
     <row r="1153">
       <c r="A1153" t="inlineStr">
@@ -40460,7 +40278,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1153" t="inlineStr"/>
       <c r="E1153" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -40493,7 +40310,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1153" t="inlineStr"/>
     </row>
     <row r="1154">
       <c r="A1154" t="inlineStr">
@@ -40511,7 +40327,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1154" t="inlineStr"/>
       <c r="E1154" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -40538,7 +40353,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1154" t="inlineStr"/>
     </row>
     <row r="1155">
       <c r="A1155" t="inlineStr">
@@ -40556,7 +40370,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1155" t="inlineStr"/>
       <c r="E1155" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -40583,7 +40396,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1155" t="inlineStr"/>
     </row>
     <row r="1156">
       <c r="A1156" t="inlineStr">
@@ -40601,7 +40413,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1156" t="inlineStr"/>
       <c r="E1156" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -40634,7 +40445,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1156" t="inlineStr"/>
     </row>
     <row r="1157">
       <c r="A1157" t="inlineStr">
@@ -40652,7 +40462,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1157" t="inlineStr"/>
       <c r="E1157" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -40679,7 +40488,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1157" t="inlineStr"/>
     </row>
     <row r="1158">
       <c r="A1158" t="inlineStr">
@@ -40697,7 +40505,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1158" t="inlineStr"/>
       <c r="E1158" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -40730,7 +40537,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1158" t="inlineStr"/>
     </row>
     <row r="1159">
       <c r="A1159" t="inlineStr">
@@ -40748,7 +40554,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1159" t="inlineStr"/>
       <c r="E1159" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -40781,7 +40586,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1159" t="inlineStr"/>
     </row>
     <row r="1160">
       <c r="A1160" t="inlineStr">
@@ -40799,7 +40603,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1160" t="inlineStr"/>
       <c r="E1160" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -40832,7 +40635,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1160" t="inlineStr"/>
     </row>
     <row r="1161">
       <c r="A1161" t="inlineStr">
@@ -40850,7 +40652,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1161" t="inlineStr"/>
       <c r="E1161" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -40883,7 +40684,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1161" t="inlineStr"/>
     </row>
     <row r="1162">
       <c r="A1162" t="inlineStr">
@@ -40901,7 +40701,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1162" t="inlineStr"/>
       <c r="E1162" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -40928,7 +40727,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1162" t="inlineStr"/>
     </row>
     <row r="1163">
       <c r="A1163" t="inlineStr">
@@ -40946,7 +40744,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1163" t="inlineStr"/>
       <c r="E1163" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -40976,7 +40773,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1163" t="inlineStr"/>
     </row>
     <row r="1164">
       <c r="A1164" t="inlineStr">
@@ -40994,7 +40790,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1164" t="inlineStr"/>
       <c r="E1164" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -41021,7 +40816,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1164" t="inlineStr"/>
     </row>
     <row r="1165">
       <c r="A1165" t="inlineStr">
@@ -41039,7 +40833,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1165" t="inlineStr"/>
       <c r="E1165" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -41072,7 +40865,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1165" t="inlineStr"/>
     </row>
     <row r="1166">
       <c r="A1166" t="inlineStr">
@@ -41090,7 +40882,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1166" t="inlineStr"/>
       <c r="E1166" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -41123,7 +40914,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1166" t="inlineStr"/>
     </row>
     <row r="1167">
       <c r="A1167" t="inlineStr">
@@ -41141,7 +40931,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1167" t="inlineStr"/>
       <c r="E1167" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -41168,7 +40957,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1167" t="inlineStr"/>
     </row>
     <row r="1168">
       <c r="A1168" t="inlineStr">
@@ -41186,7 +40974,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1168" t="inlineStr"/>
       <c r="E1168" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -41219,7 +41006,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1168" t="inlineStr"/>
     </row>
     <row r="1169">
       <c r="A1169" t="inlineStr">
@@ -41237,7 +41023,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1169" t="inlineStr"/>
       <c r="E1169" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -41270,7 +41055,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1169" t="inlineStr"/>
     </row>
     <row r="1170">
       <c r="A1170" t="inlineStr">
@@ -41288,7 +41072,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1170" t="inlineStr"/>
       <c r="E1170" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -41321,7 +41104,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1170" t="inlineStr"/>
     </row>
     <row r="1171">
       <c r="A1171" t="inlineStr">
@@ -41339,7 +41121,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1171" t="inlineStr"/>
       <c r="E1171" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -41366,7 +41147,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1171" t="inlineStr"/>
     </row>
     <row r="1172">
       <c r="A1172" t="inlineStr">
@@ -41384,7 +41164,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1172" t="inlineStr"/>
       <c r="E1172" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -41411,7 +41190,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1172" t="inlineStr"/>
     </row>
     <row r="1173">
       <c r="A1173" t="inlineStr">
@@ -41429,7 +41207,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1173" t="inlineStr"/>
       <c r="E1173" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -41456,7 +41233,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1173" t="inlineStr"/>
     </row>
     <row r="1174">
       <c r="A1174" t="inlineStr">
@@ -41474,7 +41250,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1174" t="inlineStr"/>
       <c r="E1174" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -41501,7 +41276,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1174" t="inlineStr"/>
     </row>
     <row r="1175">
       <c r="A1175" t="inlineStr">
@@ -41519,7 +41293,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1175" t="inlineStr"/>
       <c r="E1175" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -41552,7 +41325,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1175" t="inlineStr"/>
     </row>
     <row r="1176">
       <c r="A1176" t="inlineStr">
@@ -41570,7 +41342,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1176" t="inlineStr"/>
       <c r="E1176" t="inlineStr">
         <is>
           <t>Prédio Comercial</t>
@@ -41600,7 +41371,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1176" t="inlineStr"/>
     </row>
     <row r="1177">
       <c r="A1177" t="inlineStr">
@@ -41618,7 +41388,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1177" t="inlineStr"/>
       <c r="E1177" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -41651,7 +41420,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1177" t="inlineStr"/>
     </row>
     <row r="1178">
       <c r="A1178" t="inlineStr">
@@ -41669,7 +41437,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1178" t="inlineStr"/>
       <c r="E1178" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -41702,7 +41469,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1178" t="inlineStr"/>
     </row>
     <row r="1179">
       <c r="A1179" t="inlineStr">
@@ -41720,7 +41486,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1179" t="inlineStr"/>
       <c r="E1179" t="inlineStr">
         <is>
           <t>Ponto Comercial</t>
@@ -41750,7 +41515,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1179" t="inlineStr"/>
     </row>
     <row r="1180">
       <c r="A1180" t="inlineStr">
@@ -41768,7 +41532,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1180" t="inlineStr"/>
       <c r="E1180" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -41795,7 +41558,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1180" t="inlineStr"/>
     </row>
     <row r="1181">
       <c r="A1181" t="inlineStr">
@@ -41813,7 +41575,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1181" t="inlineStr"/>
       <c r="E1181" t="inlineStr">
         <is>
           <t>Prédio Comercial</t>
@@ -41846,7 +41607,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1181" t="inlineStr"/>
     </row>
     <row r="1182">
       <c r="A1182" t="inlineStr">
@@ -41864,7 +41624,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1182" t="inlineStr"/>
       <c r="E1182" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -41891,7 +41650,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1182" t="inlineStr"/>
     </row>
     <row r="1183">
       <c r="A1183" t="inlineStr">
@@ -41909,7 +41667,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1183" t="inlineStr"/>
       <c r="E1183" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -41936,7 +41693,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1183" t="inlineStr"/>
     </row>
     <row r="1184">
       <c r="A1184" t="inlineStr">
@@ -41954,7 +41710,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1184" t="inlineStr"/>
       <c r="E1184" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -41987,7 +41742,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1184" t="inlineStr"/>
     </row>
     <row r="1185">
       <c r="A1185" t="inlineStr">
@@ -42005,7 +41759,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1185" t="inlineStr"/>
       <c r="E1185" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -42038,7 +41791,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1185" t="inlineStr"/>
     </row>
     <row r="1186">
       <c r="A1186" t="inlineStr">
@@ -42056,7 +41808,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1186" t="inlineStr"/>
       <c r="E1186" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -42089,7 +41840,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1186" t="inlineStr"/>
     </row>
     <row r="1187">
       <c r="A1187" t="inlineStr">
@@ -42107,7 +41857,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1187" t="inlineStr"/>
       <c r="E1187" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -42140,7 +41889,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1187" t="inlineStr"/>
     </row>
     <row r="1188">
       <c r="A1188" t="inlineStr">
@@ -42158,7 +41906,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1188" t="inlineStr"/>
       <c r="E1188" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -42185,7 +41932,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1188" t="inlineStr"/>
     </row>
     <row r="1189">
       <c r="A1189" t="inlineStr">
@@ -42203,7 +41949,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1189" t="inlineStr"/>
       <c r="E1189" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -42230,7 +41975,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1189" t="inlineStr"/>
     </row>
     <row r="1190">
       <c r="A1190" t="inlineStr">
@@ -42248,7 +41992,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1190" t="inlineStr"/>
       <c r="E1190" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -42281,7 +42024,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1190" t="inlineStr"/>
     </row>
     <row r="1191">
       <c r="A1191" t="inlineStr">
@@ -42299,7 +42041,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1191" t="inlineStr"/>
       <c r="E1191" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -42326,7 +42067,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1191" t="inlineStr"/>
     </row>
     <row r="1192">
       <c r="A1192" t="inlineStr">
@@ -42344,7 +42084,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1192" t="inlineStr"/>
       <c r="E1192" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -42377,7 +42116,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1192" t="inlineStr"/>
     </row>
     <row r="1193">
       <c r="A1193" t="inlineStr">
@@ -42395,7 +42133,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1193" t="inlineStr"/>
       <c r="E1193" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -42422,7 +42159,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1193" t="inlineStr"/>
     </row>
     <row r="1194">
       <c r="A1194" t="inlineStr">
@@ -42440,7 +42176,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1194" t="inlineStr"/>
       <c r="E1194" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -42467,7 +42202,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1194" t="inlineStr"/>
     </row>
     <row r="1195">
       <c r="A1195" t="inlineStr">
@@ -42485,7 +42219,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1195" t="inlineStr"/>
       <c r="E1195" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -42518,7 +42251,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1195" t="inlineStr"/>
     </row>
     <row r="1196">
       <c r="A1196" t="inlineStr">
@@ -42536,7 +42268,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1196" t="inlineStr"/>
       <c r="E1196" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -42569,7 +42300,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1196" t="inlineStr"/>
     </row>
     <row r="1197">
       <c r="A1197" t="inlineStr">
@@ -42587,7 +42317,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1197" t="inlineStr"/>
       <c r="E1197" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -42614,7 +42343,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1197" t="inlineStr"/>
     </row>
     <row r="1198">
       <c r="A1198" t="inlineStr">
@@ -42632,7 +42360,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1198" t="inlineStr"/>
       <c r="E1198" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -42665,7 +42392,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1198" t="inlineStr"/>
     </row>
     <row r="1199">
       <c r="A1199" t="inlineStr">
@@ -42683,7 +42409,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1199" t="inlineStr"/>
       <c r="E1199" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -42710,7 +42435,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1199" t="inlineStr"/>
     </row>
     <row r="1200">
       <c r="A1200" t="inlineStr">
@@ -42728,7 +42452,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1200" t="inlineStr"/>
       <c r="E1200" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -42761,7 +42484,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1200" t="inlineStr"/>
     </row>
     <row r="1201">
       <c r="A1201" t="inlineStr">
@@ -42779,7 +42501,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1201" t="inlineStr"/>
       <c r="E1201" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -42812,7 +42533,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1201" t="inlineStr"/>
     </row>
     <row r="1202">
       <c r="A1202" t="inlineStr">
@@ -42830,7 +42550,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1202" t="inlineStr"/>
       <c r="E1202" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -42863,7 +42582,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1202" t="inlineStr"/>
     </row>
     <row r="1203">
       <c r="A1203" t="inlineStr">
@@ -42881,7 +42599,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1203" t="inlineStr"/>
       <c r="E1203" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -42908,7 +42625,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1203" t="inlineStr"/>
     </row>
     <row r="1204">
       <c r="A1204" t="inlineStr">
@@ -42926,7 +42642,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1204" t="inlineStr"/>
       <c r="E1204" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -42953,7 +42668,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1204" t="inlineStr"/>
     </row>
     <row r="1205">
       <c r="A1205" t="inlineStr">
@@ -42971,7 +42685,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1205" t="inlineStr"/>
       <c r="E1205" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -43004,7 +42717,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1205" t="inlineStr"/>
     </row>
     <row r="1206">
       <c r="A1206" t="inlineStr">
@@ -43022,7 +42734,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1206" t="inlineStr"/>
       <c r="E1206" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -43055,7 +42766,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1206" t="inlineStr"/>
     </row>
     <row r="1207">
       <c r="A1207" t="inlineStr">
@@ -43073,7 +42783,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1207" t="inlineStr"/>
       <c r="E1207" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -43100,7 +42809,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1207" t="inlineStr"/>
     </row>
     <row r="1208">
       <c r="A1208" t="inlineStr">
@@ -43118,7 +42826,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1208" t="inlineStr"/>
       <c r="E1208" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -43145,7 +42852,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1208" t="inlineStr"/>
     </row>
     <row r="1209">
       <c r="A1209" t="inlineStr">
@@ -43163,7 +42869,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1209" t="inlineStr"/>
       <c r="E1209" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -43193,7 +42898,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1209" t="inlineStr"/>
     </row>
     <row r="1210">
       <c r="A1210" t="inlineStr">
@@ -43211,7 +42915,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1210" t="inlineStr"/>
       <c r="E1210" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -43244,7 +42947,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1210" t="inlineStr"/>
     </row>
     <row r="1211">
       <c r="A1211" t="inlineStr">
@@ -43262,7 +42964,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1211" t="inlineStr"/>
       <c r="E1211" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -43295,7 +42996,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1211" t="inlineStr"/>
     </row>
     <row r="1212">
       <c r="A1212" t="inlineStr">
@@ -43313,7 +43013,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1212" t="inlineStr"/>
       <c r="E1212" t="inlineStr">
         <is>
           <t>Ponto Comercial</t>
@@ -43343,7 +43042,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1212" t="inlineStr"/>
     </row>
     <row r="1213">
       <c r="A1213" t="inlineStr">
@@ -43361,7 +43059,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1213" t="inlineStr"/>
       <c r="E1213" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -43394,7 +43091,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1213" t="inlineStr"/>
     </row>
     <row r="1214">
       <c r="A1214" t="inlineStr">
@@ -43412,7 +43108,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1214" t="inlineStr"/>
       <c r="E1214" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -43439,7 +43134,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1214" t="inlineStr"/>
     </row>
     <row r="1215">
       <c r="A1215" t="inlineStr">
@@ -43457,7 +43151,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1215" t="inlineStr"/>
       <c r="E1215" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -43484,7 +43177,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1215" t="inlineStr"/>
     </row>
     <row r="1216">
       <c r="A1216" t="inlineStr">
@@ -43502,7 +43194,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1216" t="inlineStr"/>
       <c r="E1216" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -43529,7 +43220,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1216" t="inlineStr"/>
     </row>
     <row r="1217">
       <c r="A1217" t="inlineStr">
@@ -43547,7 +43237,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1217" t="inlineStr"/>
       <c r="E1217" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -43580,7 +43269,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1217" t="inlineStr"/>
     </row>
     <row r="1218">
       <c r="A1218" t="inlineStr">
@@ -43598,7 +43286,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1218" t="inlineStr"/>
       <c r="E1218" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -43625,7 +43312,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1218" t="inlineStr"/>
     </row>
     <row r="1219">
       <c r="A1219" t="inlineStr">
@@ -43643,7 +43329,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1219" t="inlineStr"/>
       <c r="E1219" t="inlineStr">
         <is>
           <t>Sobrado</t>
@@ -43676,7 +43361,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1219" t="inlineStr"/>
     </row>
     <row r="1220">
       <c r="A1220" t="inlineStr">
@@ -43694,7 +43378,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1220" t="inlineStr"/>
       <c r="E1220" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -43727,7 +43410,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1220" t="inlineStr"/>
     </row>
     <row r="1221">
       <c r="A1221" t="inlineStr">
@@ -43745,7 +43427,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1221" t="inlineStr"/>
       <c r="E1221" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -43772,7 +43453,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1221" t="inlineStr"/>
     </row>
     <row r="1222">
       <c r="A1222" t="inlineStr">
@@ -43790,7 +43470,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1222" t="inlineStr"/>
       <c r="E1222" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -43817,7 +43496,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1222" t="inlineStr"/>
     </row>
     <row r="1223">
       <c r="A1223" t="inlineStr">
@@ -43835,7 +43513,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1223" t="inlineStr"/>
       <c r="E1223" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -43865,7 +43542,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1223" t="inlineStr"/>
     </row>
     <row r="1224">
       <c r="A1224" t="inlineStr">
@@ -43883,7 +43559,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1224" t="inlineStr"/>
       <c r="E1224" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -43913,7 +43588,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1224" t="inlineStr"/>
     </row>
     <row r="1225">
       <c r="A1225" t="inlineStr">
@@ -43931,7 +43605,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1225" t="inlineStr"/>
       <c r="E1225" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -43958,7 +43631,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1225" t="inlineStr"/>
     </row>
     <row r="1226">
       <c r="A1226" t="inlineStr">
@@ -43976,7 +43648,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1226" t="inlineStr"/>
       <c r="E1226" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -44009,7 +43680,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1226" t="inlineStr"/>
     </row>
     <row r="1227">
       <c r="A1227" t="inlineStr">
@@ -44027,7 +43697,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1227" t="inlineStr"/>
       <c r="E1227" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -44060,7 +43729,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1227" t="inlineStr"/>
     </row>
     <row r="1228">
       <c r="A1228" t="inlineStr">
@@ -44078,7 +43746,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1228" t="inlineStr"/>
       <c r="E1228" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -44111,7 +43778,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1228" t="inlineStr"/>
     </row>
     <row r="1229">
       <c r="A1229" t="inlineStr">
@@ -44129,7 +43795,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1229" t="inlineStr"/>
       <c r="E1229" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -44162,7 +43827,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1229" t="inlineStr"/>
     </row>
     <row r="1230">
       <c r="A1230" t="inlineStr">
@@ -44180,7 +43844,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1230" t="inlineStr"/>
       <c r="E1230" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -44207,7 +43870,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1230" t="inlineStr"/>
     </row>
     <row r="1231">
       <c r="A1231" t="inlineStr">
@@ -44225,7 +43887,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1231" t="inlineStr"/>
       <c r="E1231" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -44252,7 +43913,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1231" t="inlineStr"/>
     </row>
     <row r="1232">
       <c r="A1232" t="inlineStr">
@@ -44270,7 +43930,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1232" t="inlineStr"/>
       <c r="E1232" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -44303,7 +43962,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1232" t="inlineStr"/>
     </row>
     <row r="1233">
       <c r="A1233" t="inlineStr">
@@ -44321,7 +43979,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1233" t="inlineStr"/>
       <c r="E1233" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -44348,7 +44005,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1233" t="inlineStr"/>
     </row>
     <row r="1234">
       <c r="A1234" t="inlineStr">
@@ -44366,7 +44022,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1234" t="inlineStr"/>
       <c r="E1234" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -44393,7 +44048,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1234" t="inlineStr"/>
     </row>
     <row r="1235">
       <c r="A1235" t="inlineStr">
@@ -44411,7 +44065,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1235" t="inlineStr"/>
       <c r="E1235" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -44441,7 +44094,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1235" t="inlineStr"/>
     </row>
     <row r="1236">
       <c r="A1236" t="inlineStr">
@@ -44459,7 +44111,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1236" t="inlineStr"/>
       <c r="E1236" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -44486,7 +44137,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1236" t="inlineStr"/>
     </row>
     <row r="1237">
       <c r="A1237" t="inlineStr">
@@ -44504,7 +44154,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1237" t="inlineStr"/>
       <c r="E1237" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -44534,7 +44183,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1237" t="inlineStr"/>
     </row>
     <row r="1238">
       <c r="A1238" t="inlineStr">
@@ -44552,7 +44200,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1238" t="inlineStr"/>
       <c r="E1238" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -44579,7 +44226,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1238" t="inlineStr"/>
     </row>
     <row r="1239">
       <c r="A1239" t="inlineStr">
@@ -44597,7 +44243,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1239" t="inlineStr"/>
       <c r="E1239" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -44630,7 +44275,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1239" t="inlineStr"/>
     </row>
     <row r="1240">
       <c r="A1240" t="inlineStr">
@@ -44648,7 +44292,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1240" t="inlineStr"/>
       <c r="E1240" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -44675,7 +44318,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1240" t="inlineStr"/>
     </row>
     <row r="1241">
       <c r="A1241" t="inlineStr">
@@ -44693,7 +44335,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1241" t="inlineStr"/>
       <c r="E1241" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -44723,7 +44364,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1241" t="inlineStr"/>
     </row>
     <row r="1242">
       <c r="A1242" t="inlineStr">
@@ -44741,7 +44381,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1242" t="inlineStr"/>
       <c r="E1242" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -44774,7 +44413,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1242" t="inlineStr"/>
     </row>
     <row r="1243">
       <c r="A1243" t="inlineStr">
@@ -44792,7 +44430,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1243" t="inlineStr"/>
       <c r="E1243" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -44819,7 +44456,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1243" t="inlineStr"/>
     </row>
     <row r="1244">
       <c r="A1244" t="inlineStr">
@@ -44837,7 +44473,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1244" t="inlineStr"/>
       <c r="E1244" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -44870,7 +44505,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1244" t="inlineStr"/>
     </row>
     <row r="1245">
       <c r="A1245" t="inlineStr">
@@ -44888,7 +44522,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1245" t="inlineStr"/>
       <c r="E1245" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -44915,7 +44548,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1245" t="inlineStr"/>
     </row>
     <row r="1246">
       <c r="A1246" t="inlineStr">
@@ -44933,7 +44565,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1246" t="inlineStr"/>
       <c r="E1246" t="inlineStr">
         <is>
           <t>Prédio Comercial</t>
@@ -44960,7 +44591,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1246" t="inlineStr"/>
     </row>
     <row r="1247">
       <c r="A1247" t="inlineStr">
@@ -44978,7 +44608,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1247" t="inlineStr"/>
       <c r="E1247" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -45011,7 +44640,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1247" t="inlineStr"/>
     </row>
     <row r="1248">
       <c r="A1248" t="inlineStr">
@@ -45029,7 +44657,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1248" t="inlineStr"/>
       <c r="E1248" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -45062,7 +44689,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1248" t="inlineStr"/>
     </row>
     <row r="1249">
       <c r="A1249" t="inlineStr">
@@ -45080,7 +44706,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1249" t="inlineStr"/>
       <c r="E1249" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -45113,7 +44738,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1249" t="inlineStr"/>
     </row>
     <row r="1250">
       <c r="A1250" t="inlineStr">
@@ -45131,7 +44755,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1250" t="inlineStr"/>
       <c r="E1250" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -45164,7 +44787,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1250" t="inlineStr"/>
     </row>
     <row r="1251">
       <c r="A1251" t="inlineStr">
@@ -45182,7 +44804,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1251" t="inlineStr"/>
       <c r="E1251" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -45209,7 +44830,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1251" t="inlineStr"/>
     </row>
     <row r="1252">
       <c r="A1252" t="inlineStr">
@@ -45227,7 +44847,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1252" t="inlineStr"/>
       <c r="E1252" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -45260,7 +44879,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1252" t="inlineStr"/>
     </row>
     <row r="1253">
       <c r="A1253" t="inlineStr">
@@ -45278,7 +44896,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1253" t="inlineStr"/>
       <c r="E1253" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -45305,7 +44922,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1253" t="inlineStr"/>
     </row>
     <row r="1254">
       <c r="A1254" t="inlineStr">
@@ -45323,7 +44939,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1254" t="inlineStr"/>
       <c r="E1254" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -45350,7 +44965,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1254" t="inlineStr"/>
     </row>
     <row r="1255">
       <c r="A1255" t="inlineStr">
@@ -45368,7 +44982,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1255" t="inlineStr"/>
       <c r="E1255" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -45395,7 +45008,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1255" t="inlineStr"/>
     </row>
     <row r="1256">
       <c r="A1256" t="inlineStr">
@@ -45413,7 +45025,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1256" t="inlineStr"/>
       <c r="E1256" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -45440,7 +45051,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1256" t="inlineStr"/>
     </row>
     <row r="1257">
       <c r="A1257" t="inlineStr">
@@ -45458,7 +45068,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1257" t="inlineStr"/>
       <c r="E1257" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -45485,7 +45094,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1257" t="inlineStr"/>
     </row>
     <row r="1258">
       <c r="A1258" t="inlineStr">
@@ -45503,7 +45111,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1258" t="inlineStr"/>
       <c r="E1258" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -45530,7 +45137,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1258" t="inlineStr"/>
     </row>
     <row r="1259">
       <c r="A1259" t="inlineStr">
@@ -45548,7 +45154,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1259" t="inlineStr"/>
       <c r="E1259" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -45575,7 +45180,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1259" t="inlineStr"/>
     </row>
     <row r="1260">
       <c r="A1260" t="inlineStr">
@@ -45593,7 +45197,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1260" t="inlineStr"/>
       <c r="E1260" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -45620,7 +45223,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1260" t="inlineStr"/>
     </row>
     <row r="1261">
       <c r="A1261" t="inlineStr">
@@ -45638,7 +45240,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1261" t="inlineStr"/>
       <c r="E1261" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -45671,7 +45272,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1261" t="inlineStr"/>
     </row>
     <row r="1262">
       <c r="A1262" t="inlineStr">
@@ -45689,7 +45289,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1262" t="inlineStr"/>
       <c r="E1262" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -45716,7 +45315,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1262" t="inlineStr"/>
     </row>
     <row r="1263">
       <c r="A1263" t="inlineStr">
@@ -45734,7 +45332,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1263" t="inlineStr"/>
       <c r="E1263" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -45761,7 +45358,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1263" t="inlineStr"/>
     </row>
     <row r="1264">
       <c r="A1264" t="inlineStr">
@@ -45779,7 +45375,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1264" t="inlineStr"/>
       <c r="E1264" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -45806,7 +45401,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1264" t="inlineStr"/>
     </row>
     <row r="1265">
       <c r="A1265" t="inlineStr">
@@ -45824,7 +45418,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1265" t="inlineStr"/>
       <c r="E1265" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -45857,7 +45450,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1265" t="inlineStr"/>
     </row>
     <row r="1266">
       <c r="A1266" t="inlineStr">
@@ -45875,7 +45467,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1266" t="inlineStr"/>
       <c r="E1266" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -45902,7 +45493,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1266" t="inlineStr"/>
     </row>
     <row r="1267">
       <c r="A1267" t="inlineStr">
@@ -45920,7 +45510,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1267" t="inlineStr"/>
       <c r="E1267" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -45953,7 +45542,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1267" t="inlineStr"/>
     </row>
     <row r="1268">
       <c r="A1268" t="inlineStr">
@@ -45971,7 +45559,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1268" t="inlineStr"/>
       <c r="E1268" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -45998,7 +45585,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1268" t="inlineStr"/>
     </row>
     <row r="1269">
       <c r="A1269" t="inlineStr">
@@ -46016,7 +45602,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1269" t="inlineStr"/>
       <c r="E1269" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -46043,7 +45628,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1269" t="inlineStr"/>
     </row>
     <row r="1270">
       <c r="A1270" t="inlineStr">
@@ -46061,7 +45645,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1270" t="inlineStr"/>
       <c r="E1270" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -46091,7 +45674,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1270" t="inlineStr"/>
     </row>
     <row r="1271">
       <c r="A1271" t="inlineStr">
@@ -46109,7 +45691,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1271" t="inlineStr"/>
       <c r="E1271" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -46142,7 +45723,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1271" t="inlineStr"/>
     </row>
     <row r="1272">
       <c r="A1272" t="inlineStr">
@@ -46160,7 +45740,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1272" t="inlineStr"/>
       <c r="E1272" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -46193,7 +45772,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1272" t="inlineStr"/>
     </row>
     <row r="1273">
       <c r="A1273" t="inlineStr">
@@ -46211,7 +45789,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1273" t="inlineStr"/>
       <c r="E1273" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -46241,7 +45818,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1273" t="inlineStr"/>
     </row>
     <row r="1274">
       <c r="A1274" t="inlineStr">
@@ -46259,7 +45835,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1274" t="inlineStr"/>
       <c r="E1274" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -46286,7 +45861,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1274" t="inlineStr"/>
     </row>
     <row r="1275">
       <c r="A1275" t="inlineStr">
@@ -46304,7 +45878,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1275" t="inlineStr"/>
       <c r="E1275" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -46331,7 +45904,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1275" t="inlineStr"/>
     </row>
     <row r="1276">
       <c r="A1276" t="inlineStr">
@@ -46349,7 +45921,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1276" t="inlineStr"/>
       <c r="E1276" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -46382,7 +45953,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1276" t="inlineStr"/>
     </row>
     <row r="1277">
       <c r="A1277" t="inlineStr">
@@ -46400,7 +45970,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1277" t="inlineStr"/>
       <c r="E1277" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -46433,7 +46002,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1277" t="inlineStr"/>
     </row>
     <row r="1278">
       <c r="A1278" t="inlineStr">
@@ -46451,7 +46019,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1278" t="inlineStr"/>
       <c r="E1278" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -46484,7 +46051,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1278" t="inlineStr"/>
     </row>
     <row r="1279">
       <c r="A1279" t="inlineStr">
@@ -46502,7 +46068,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1279" t="inlineStr"/>
       <c r="E1279" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -46535,7 +46100,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1279" t="inlineStr"/>
     </row>
     <row r="1280">
       <c r="A1280" t="inlineStr">
@@ -46553,7 +46117,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1280" t="inlineStr"/>
       <c r="E1280" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -46586,7 +46149,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1280" t="inlineStr"/>
     </row>
     <row r="1281">
       <c r="A1281" t="inlineStr">
@@ -46604,7 +46166,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1281" t="inlineStr"/>
       <c r="E1281" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -46637,7 +46198,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1281" t="inlineStr"/>
     </row>
     <row r="1282">
       <c r="A1282" t="inlineStr">
@@ -46655,7 +46215,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1282" t="inlineStr"/>
       <c r="E1282" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -46688,7 +46247,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1282" t="inlineStr"/>
     </row>
     <row r="1283">
       <c r="A1283" t="inlineStr">
@@ -46706,7 +46264,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1283" t="inlineStr"/>
       <c r="E1283" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -46739,7 +46296,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1283" t="inlineStr"/>
     </row>
     <row r="1284">
       <c r="A1284" t="inlineStr">
@@ -46757,7 +46313,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1284" t="inlineStr"/>
       <c r="E1284" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -46790,7 +46345,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1284" t="inlineStr"/>
     </row>
     <row r="1285">
       <c r="A1285" t="inlineStr">
@@ -46808,7 +46362,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1285" t="inlineStr"/>
       <c r="E1285" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -46835,7 +46388,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1285" t="inlineStr"/>
     </row>
     <row r="1286">
       <c r="A1286" t="inlineStr">
@@ -46853,7 +46405,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1286" t="inlineStr"/>
       <c r="E1286" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -46880,7 +46431,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1286" t="inlineStr"/>
     </row>
     <row r="1287">
       <c r="A1287" t="inlineStr">
@@ -46898,7 +46448,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1287" t="inlineStr"/>
       <c r="E1287" t="inlineStr">
         <is>
           <t>Prédio Comercial</t>
@@ -46928,7 +46477,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1287" t="inlineStr"/>
     </row>
     <row r="1288">
       <c r="A1288" t="inlineStr">
@@ -46946,7 +46494,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1288" t="inlineStr"/>
       <c r="E1288" t="inlineStr">
         <is>
           <t>Prédio Comercial</t>
@@ -46976,7 +46523,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1288" t="inlineStr"/>
     </row>
     <row r="1289">
       <c r="A1289" t="inlineStr">
@@ -46994,7 +46540,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1289" t="inlineStr"/>
       <c r="E1289" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -47021,7 +46566,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1289" t="inlineStr"/>
     </row>
     <row r="1290">
       <c r="A1290" t="inlineStr">
@@ -47039,7 +46583,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1290" t="inlineStr"/>
       <c r="E1290" t="inlineStr">
         <is>
           <t>Sala Comercial</t>
@@ -47072,7 +46615,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1290" t="inlineStr"/>
     </row>
     <row r="1291">
       <c r="A1291" t="inlineStr">
@@ -47090,7 +46632,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1291" t="inlineStr"/>
       <c r="E1291" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -47117,7 +46658,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1291" t="inlineStr"/>
     </row>
     <row r="1292">
       <c r="A1292" t="inlineStr">
@@ -47135,7 +46675,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1292" t="inlineStr"/>
       <c r="E1292" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -47162,7 +46701,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1292" t="inlineStr"/>
     </row>
     <row r="1293">
       <c r="A1293" t="inlineStr">
@@ -47180,7 +46718,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1293" t="inlineStr"/>
       <c r="E1293" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -47213,7 +46750,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1293" t="inlineStr"/>
     </row>
     <row r="1294">
       <c r="A1294" t="inlineStr">
@@ -47231,7 +46767,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1294" t="inlineStr"/>
       <c r="E1294" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -47258,7 +46793,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1294" t="inlineStr"/>
     </row>
     <row r="1295">
       <c r="A1295" t="inlineStr">
@@ -47276,7 +46810,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1295" t="inlineStr"/>
       <c r="E1295" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -47303,7 +46836,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1295" t="inlineStr"/>
     </row>
     <row r="1296">
       <c r="A1296" t="inlineStr">
@@ -47321,7 +46853,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1296" t="inlineStr"/>
       <c r="E1296" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -47348,7 +46879,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1296" t="inlineStr"/>
     </row>
     <row r="1297">
       <c r="A1297" t="inlineStr">
@@ -47366,7 +46896,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1297" t="inlineStr"/>
       <c r="E1297" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -47399,7 +46928,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1297" t="inlineStr"/>
     </row>
     <row r="1298">
       <c r="A1298" t="inlineStr">
@@ -47417,7 +46945,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1298" t="inlineStr"/>
       <c r="E1298" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -47450,7 +46977,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1298" t="inlineStr"/>
     </row>
     <row r="1299">
       <c r="A1299" t="inlineStr">
@@ -47468,7 +46994,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1299" t="inlineStr"/>
       <c r="E1299" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -47501,7 +47026,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1299" t="inlineStr"/>
     </row>
     <row r="1300">
       <c r="A1300" t="inlineStr">
@@ -47519,7 +47043,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1300" t="inlineStr"/>
       <c r="E1300" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -47546,7 +47069,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1300" t="inlineStr"/>
     </row>
     <row r="1301">
       <c r="A1301" t="inlineStr">
@@ -47564,7 +47086,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1301" t="inlineStr"/>
       <c r="E1301" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -47597,7 +47118,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1301" t="inlineStr"/>
     </row>
     <row r="1302">
       <c r="A1302" t="inlineStr">
@@ -47615,7 +47135,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1302" t="inlineStr"/>
       <c r="E1302" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -47648,7 +47167,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1302" t="inlineStr"/>
     </row>
     <row r="1303">
       <c r="A1303" t="inlineStr">
@@ -47666,7 +47184,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1303" t="inlineStr"/>
       <c r="E1303" t="inlineStr">
         <is>
           <t>Prédio Comercial</t>
@@ -47693,7 +47210,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1303" t="inlineStr"/>
     </row>
     <row r="1304">
       <c r="A1304" t="inlineStr">
@@ -47711,7 +47227,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1304" t="inlineStr"/>
       <c r="E1304" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -47744,7 +47259,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1304" t="inlineStr"/>
     </row>
     <row r="1305">
       <c r="A1305" t="inlineStr">
@@ -47762,7 +47276,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1305" t="inlineStr"/>
       <c r="E1305" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -47792,7 +47305,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1305" t="inlineStr"/>
     </row>
     <row r="1306">
       <c r="A1306" t="inlineStr">
@@ -47810,7 +47322,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1306" t="inlineStr"/>
       <c r="E1306" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -47843,7 +47354,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1306" t="inlineStr"/>
     </row>
     <row r="1307">
       <c r="A1307" t="inlineStr">
@@ -47861,7 +47371,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1307" t="inlineStr"/>
       <c r="E1307" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -47894,7 +47403,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1307" t="inlineStr"/>
     </row>
     <row r="1308">
       <c r="A1308" t="inlineStr">
@@ -47912,7 +47420,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1308" t="inlineStr"/>
       <c r="E1308" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -47945,7 +47452,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1308" t="inlineStr"/>
     </row>
     <row r="1309">
       <c r="A1309" t="inlineStr">
@@ -47963,7 +47469,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1309" t="inlineStr"/>
       <c r="E1309" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -47996,7 +47501,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1309" t="inlineStr"/>
     </row>
     <row r="1310">
       <c r="A1310" t="inlineStr">
@@ -48014,7 +47518,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1310" t="inlineStr"/>
       <c r="E1310" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -48041,7 +47544,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1310" t="inlineStr"/>
     </row>
     <row r="1311">
       <c r="A1311" t="inlineStr">
@@ -48059,7 +47561,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1311" t="inlineStr"/>
       <c r="E1311" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -48086,7 +47587,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1311" t="inlineStr"/>
     </row>
     <row r="1312">
       <c r="A1312" t="inlineStr">
@@ -48104,7 +47604,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1312" t="inlineStr"/>
       <c r="E1312" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -48131,7 +47630,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1312" t="inlineStr"/>
     </row>
     <row r="1313">
       <c r="A1313" t="inlineStr">
@@ -48149,7 +47647,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1313" t="inlineStr"/>
       <c r="E1313" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -48182,7 +47679,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1313" t="inlineStr"/>
     </row>
     <row r="1314">
       <c r="A1314" t="inlineStr">
@@ -48200,7 +47696,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1314" t="inlineStr"/>
       <c r="E1314" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -48230,7 +47725,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1314" t="inlineStr"/>
     </row>
     <row r="1315">
       <c r="A1315" t="inlineStr">
@@ -48248,7 +47742,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1315" t="inlineStr"/>
       <c r="E1315" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -48278,7 +47771,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1315" t="inlineStr"/>
     </row>
     <row r="1316">
       <c r="A1316" t="inlineStr">
@@ -48296,7 +47788,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1316" t="inlineStr"/>
       <c r="E1316" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -48329,7 +47820,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1316" t="inlineStr"/>
     </row>
     <row r="1317">
       <c r="A1317" t="inlineStr">
@@ -48347,7 +47837,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1317" t="inlineStr"/>
       <c r="E1317" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -48380,7 +47869,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1317" t="inlineStr"/>
     </row>
     <row r="1318">
       <c r="A1318" t="inlineStr">
@@ -48398,7 +47886,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1318" t="inlineStr"/>
       <c r="E1318" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -48425,7 +47912,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1318" t="inlineStr"/>
     </row>
     <row r="1319">
       <c r="A1319" t="inlineStr">
@@ -48443,7 +47929,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1319" t="inlineStr"/>
       <c r="E1319" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -48470,7 +47955,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1319" t="inlineStr"/>
     </row>
     <row r="1320">
       <c r="A1320" t="inlineStr">
@@ -48488,7 +47972,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1320" t="inlineStr"/>
       <c r="E1320" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -48521,7 +48004,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1320" t="inlineStr"/>
     </row>
     <row r="1321">
       <c r="A1321" t="inlineStr">
@@ -48539,7 +48021,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1321" t="inlineStr"/>
       <c r="E1321" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -48572,7 +48053,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1321" t="inlineStr"/>
     </row>
     <row r="1322">
       <c r="A1322" t="inlineStr">
@@ -48590,7 +48070,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1322" t="inlineStr"/>
       <c r="E1322" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -48617,7 +48096,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1322" t="inlineStr"/>
     </row>
     <row r="1323">
       <c r="A1323" t="inlineStr">
@@ -48635,7 +48113,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1323" t="inlineStr"/>
       <c r="E1323" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -48665,7 +48142,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1323" t="inlineStr"/>
     </row>
     <row r="1324">
       <c r="A1324" t="inlineStr">
@@ -48683,7 +48159,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1324" t="inlineStr"/>
       <c r="E1324" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -48716,7 +48191,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1324" t="inlineStr"/>
     </row>
     <row r="1325">
       <c r="A1325" t="inlineStr">
@@ -48734,7 +48208,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1325" t="inlineStr"/>
       <c r="E1325" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -48761,7 +48234,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1325" t="inlineStr"/>
     </row>
     <row r="1326">
       <c r="A1326" t="inlineStr">
@@ -48779,7 +48251,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1326" t="inlineStr"/>
       <c r="E1326" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -48806,7 +48277,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1326" t="inlineStr"/>
     </row>
     <row r="1327">
       <c r="A1327" t="inlineStr">
@@ -48824,7 +48294,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1327" t="inlineStr"/>
       <c r="E1327" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -48857,7 +48326,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1327" t="inlineStr"/>
     </row>
     <row r="1328">
       <c r="A1328" t="inlineStr">
@@ -48875,7 +48343,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1328" t="inlineStr"/>
       <c r="E1328" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -48908,7 +48375,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1328" t="inlineStr"/>
     </row>
     <row r="1329">
       <c r="A1329" t="inlineStr">
@@ -48926,7 +48392,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1329" t="inlineStr"/>
       <c r="E1329" t="inlineStr">
         <is>
           <t>Sobrado</t>
@@ -48956,7 +48421,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1329" t="inlineStr"/>
     </row>
     <row r="1330">
       <c r="A1330" t="inlineStr">
@@ -48974,7 +48438,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1330" t="inlineStr"/>
       <c r="E1330" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -49001,7 +48464,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1330" t="inlineStr"/>
     </row>
     <row r="1331">
       <c r="A1331" t="inlineStr">
@@ -49019,7 +48481,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1331" t="inlineStr"/>
       <c r="E1331" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -49052,7 +48513,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1331" t="inlineStr"/>
     </row>
     <row r="1332">
       <c r="A1332" t="inlineStr">
@@ -49070,7 +48530,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1332" t="inlineStr"/>
       <c r="E1332" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -49103,7 +48562,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1332" t="inlineStr"/>
     </row>
     <row r="1333">
       <c r="A1333" t="inlineStr">
@@ -49121,7 +48579,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1333" t="inlineStr"/>
       <c r="E1333" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -49154,7 +48611,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1333" t="inlineStr"/>
     </row>
     <row r="1334">
       <c r="A1334" t="inlineStr">
@@ -49172,7 +48628,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1334" t="inlineStr"/>
       <c r="E1334" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -49205,7 +48660,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1334" t="inlineStr"/>
     </row>
     <row r="1335">
       <c r="A1335" t="inlineStr">
@@ -49223,7 +48677,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1335" t="inlineStr"/>
       <c r="E1335" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -49256,7 +48709,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1335" t="inlineStr"/>
     </row>
     <row r="1336">
       <c r="A1336" t="inlineStr">
@@ -49274,7 +48726,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1336" t="inlineStr"/>
       <c r="E1336" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -49307,7 +48758,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1336" t="inlineStr"/>
     </row>
     <row r="1337">
       <c r="A1337" t="inlineStr">
@@ -49325,7 +48775,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1337" t="inlineStr"/>
       <c r="E1337" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -49358,7 +48807,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1337" t="inlineStr"/>
     </row>
     <row r="1338">
       <c r="A1338" t="inlineStr">
@@ -49376,7 +48824,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1338" t="inlineStr"/>
       <c r="E1338" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -49403,7 +48850,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1338" t="inlineStr"/>
     </row>
     <row r="1339">
       <c r="A1339" t="inlineStr">
@@ -49421,7 +48867,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1339" t="inlineStr"/>
       <c r="E1339" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -49454,7 +48899,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1339" t="inlineStr"/>
     </row>
     <row r="1340">
       <c r="A1340" t="inlineStr">
@@ -49472,7 +48916,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1340" t="inlineStr"/>
       <c r="E1340" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -49502,7 +48945,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1340" t="inlineStr"/>
     </row>
     <row r="1341">
       <c r="A1341" t="inlineStr">
@@ -49520,7 +48962,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1341" t="inlineStr"/>
       <c r="E1341" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -49547,7 +48988,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1341" t="inlineStr"/>
     </row>
     <row r="1342">
       <c r="A1342" t="inlineStr">
@@ -49565,7 +49005,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1342" t="inlineStr"/>
       <c r="E1342" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -49592,7 +49031,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1342" t="inlineStr"/>
     </row>
     <row r="1343">
       <c r="A1343" t="inlineStr">
@@ -49610,13 +49048,11 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1343" t="inlineStr"/>
       <c r="E1343" t="inlineStr">
         <is>
           <t>Imóvel Comercial</t>
         </is>
       </c>
-      <c r="F1343" t="inlineStr"/>
       <c r="G1343" t="n">
         <v>180</v>
       </c>
@@ -49636,7 +49072,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1343" t="inlineStr"/>
     </row>
     <row r="1344">
       <c r="A1344" t="inlineStr">
@@ -49654,7 +49089,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1344" t="inlineStr"/>
       <c r="E1344" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -49687,7 +49121,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1344" t="inlineStr"/>
     </row>
     <row r="1345">
       <c r="A1345" t="inlineStr">
@@ -49705,7 +49138,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1345" t="inlineStr"/>
       <c r="E1345" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -49735,7 +49167,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1345" t="inlineStr"/>
     </row>
     <row r="1346">
       <c r="A1346" t="inlineStr">
@@ -49753,7 +49184,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1346" t="inlineStr"/>
       <c r="E1346" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -49780,7 +49210,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1346" t="inlineStr"/>
     </row>
     <row r="1347">
       <c r="A1347" t="inlineStr">
@@ -49798,7 +49227,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1347" t="inlineStr"/>
       <c r="E1347" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -49831,7 +49259,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1347" t="inlineStr"/>
     </row>
     <row r="1348">
       <c r="A1348" t="inlineStr">
@@ -49849,7 +49276,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1348" t="inlineStr"/>
       <c r="E1348" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -49876,7 +49302,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1348" t="inlineStr"/>
     </row>
     <row r="1349">
       <c r="A1349" t="inlineStr">
@@ -49894,7 +49319,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1349" t="inlineStr"/>
       <c r="E1349" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -49927,7 +49351,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1349" t="inlineStr"/>
     </row>
     <row r="1350">
       <c r="A1350" t="inlineStr">
@@ -49945,7 +49368,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1350" t="inlineStr"/>
       <c r="E1350" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -49972,7 +49394,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1350" t="inlineStr"/>
     </row>
     <row r="1351">
       <c r="A1351" t="inlineStr">
@@ -49990,7 +49411,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1351" t="inlineStr"/>
       <c r="E1351" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -50020,7 +49440,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1351" t="inlineStr"/>
     </row>
     <row r="1352">
       <c r="A1352" t="inlineStr">
@@ -50038,7 +49457,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1352" t="inlineStr"/>
       <c r="E1352" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -50071,7 +49489,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1352" t="inlineStr"/>
     </row>
     <row r="1353">
       <c r="A1353" t="inlineStr">
@@ -50089,7 +49506,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1353" t="inlineStr"/>
       <c r="E1353" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -50122,7 +49538,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1353" t="inlineStr"/>
     </row>
     <row r="1354">
       <c r="A1354" t="inlineStr">
@@ -50140,7 +49555,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1354" t="inlineStr"/>
       <c r="E1354" t="inlineStr">
         <is>
           <t>Imóvel Comercial</t>
@@ -50173,7 +49587,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1354" t="inlineStr"/>
     </row>
     <row r="1355">
       <c r="A1355" t="inlineStr">
@@ -50191,7 +49604,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1355" t="inlineStr"/>
       <c r="E1355" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -50224,7 +49636,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1355" t="inlineStr"/>
     </row>
     <row r="1356">
       <c r="A1356" t="inlineStr">
@@ -50242,7 +49653,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1356" t="inlineStr"/>
       <c r="E1356" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -50272,7 +49682,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1356" t="inlineStr"/>
     </row>
     <row r="1357">
       <c r="A1357" t="inlineStr">
@@ -50290,7 +49699,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1357" t="inlineStr"/>
       <c r="E1357" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -50323,7 +49731,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1357" t="inlineStr"/>
     </row>
     <row r="1358">
       <c r="A1358" t="inlineStr">
@@ -50341,7 +49748,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1358" t="inlineStr"/>
       <c r="E1358" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -50374,7 +49780,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1358" t="inlineStr"/>
     </row>
     <row r="1359">
       <c r="A1359" t="inlineStr">
@@ -50392,7 +49797,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1359" t="inlineStr"/>
       <c r="E1359" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -50425,7 +49829,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1359" t="inlineStr"/>
     </row>
     <row r="1360">
       <c r="A1360" t="inlineStr">
@@ -50443,7 +49846,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1360" t="inlineStr"/>
       <c r="E1360" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -50473,7 +49875,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1360" t="inlineStr"/>
     </row>
     <row r="1361">
       <c r="A1361" t="inlineStr">
@@ -50491,7 +49892,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1361" t="inlineStr"/>
       <c r="E1361" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -50518,7 +49918,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1361" t="inlineStr"/>
     </row>
     <row r="1362">
       <c r="A1362" t="inlineStr">
@@ -50536,7 +49935,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1362" t="inlineStr"/>
       <c r="E1362" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -50569,7 +49967,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1362" t="inlineStr"/>
     </row>
     <row r="1363">
       <c r="A1363" t="inlineStr">
@@ -50587,7 +49984,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1363" t="inlineStr"/>
       <c r="E1363" t="inlineStr">
         <is>
           <t>Prédio Comercial</t>
@@ -50620,7 +50016,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1363" t="inlineStr"/>
     </row>
     <row r="1364">
       <c r="A1364" t="inlineStr">
@@ -50638,7 +50033,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1364" t="inlineStr"/>
       <c r="E1364" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -50665,7 +50059,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1364" t="inlineStr"/>
     </row>
     <row r="1365">
       <c r="A1365" t="inlineStr">
@@ -50683,7 +50076,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1365" t="inlineStr"/>
       <c r="E1365" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -50716,7 +50108,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1365" t="inlineStr"/>
     </row>
     <row r="1366">
       <c r="A1366" t="inlineStr">
@@ -50734,7 +50125,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1366" t="inlineStr"/>
       <c r="E1366" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -50761,7 +50151,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1366" t="inlineStr"/>
     </row>
     <row r="1367">
       <c r="A1367" t="inlineStr">
@@ -50779,7 +50168,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1367" t="inlineStr"/>
       <c r="E1367" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -50812,7 +50200,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1367" t="inlineStr"/>
     </row>
     <row r="1368">
       <c r="A1368" t="inlineStr">
@@ -50830,7 +50217,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1368" t="inlineStr"/>
       <c r="E1368" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -50857,7 +50243,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1368" t="inlineStr"/>
     </row>
     <row r="1369">
       <c r="A1369" t="inlineStr">
@@ -50875,7 +50260,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1369" t="inlineStr"/>
       <c r="E1369" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -50902,7 +50286,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1369" t="inlineStr"/>
     </row>
     <row r="1370">
       <c r="A1370" t="inlineStr">
@@ -50920,7 +50303,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1370" t="inlineStr"/>
       <c r="E1370" t="inlineStr">
         <is>
           <t>Sobrado</t>
@@ -50950,7 +50332,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1370" t="inlineStr"/>
     </row>
     <row r="1371">
       <c r="A1371" t="inlineStr">
@@ -50968,7 +50349,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1371" t="inlineStr"/>
       <c r="E1371" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -51001,7 +50381,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1371" t="inlineStr"/>
     </row>
     <row r="1372">
       <c r="A1372" t="inlineStr">
@@ -51019,7 +50398,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1372" t="inlineStr"/>
       <c r="E1372" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -51046,7 +50424,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1372" t="inlineStr"/>
     </row>
     <row r="1373">
       <c r="A1373" t="inlineStr">
@@ -51064,7 +50441,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1373" t="inlineStr"/>
       <c r="E1373" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -51097,7 +50473,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1373" t="inlineStr"/>
     </row>
     <row r="1374">
       <c r="A1374" t="inlineStr">
@@ -51115,7 +50490,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1374" t="inlineStr"/>
       <c r="E1374" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -51142,7 +50516,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1374" t="inlineStr"/>
     </row>
     <row r="1375">
       <c r="A1375" t="inlineStr">
@@ -51160,7 +50533,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1375" t="inlineStr"/>
       <c r="E1375" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -51193,7 +50565,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1375" t="inlineStr"/>
     </row>
     <row r="1376">
       <c r="A1376" t="inlineStr">
@@ -51211,7 +50582,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1376" t="inlineStr"/>
       <c r="E1376" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -51238,7 +50608,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1376" t="inlineStr"/>
     </row>
     <row r="1377">
       <c r="A1377" t="inlineStr">
@@ -51256,7 +50625,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1377" t="inlineStr"/>
       <c r="E1377" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -51289,7 +50657,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1377" t="inlineStr"/>
     </row>
     <row r="1378">
       <c r="A1378" t="inlineStr">
@@ -51307,7 +50674,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1378" t="inlineStr"/>
       <c r="E1378" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -51340,7 +50706,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1378" t="inlineStr"/>
     </row>
     <row r="1379">
       <c r="A1379" t="inlineStr">
@@ -51358,7 +50723,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1379" t="inlineStr"/>
       <c r="E1379" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -51391,7 +50755,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1379" t="inlineStr"/>
     </row>
     <row r="1380">
       <c r="A1380" t="inlineStr">
@@ -51409,7 +50772,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1380" t="inlineStr"/>
       <c r="E1380" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -51442,7 +50804,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1380" t="inlineStr"/>
     </row>
     <row r="1381">
       <c r="A1381" t="inlineStr">
@@ -51460,7 +50821,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1381" t="inlineStr"/>
       <c r="E1381" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -51493,7 +50853,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1381" t="inlineStr"/>
     </row>
     <row r="1382">
       <c r="A1382" t="inlineStr">
@@ -51511,7 +50870,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1382" t="inlineStr"/>
       <c r="E1382" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -51544,7 +50902,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1382" t="inlineStr"/>
     </row>
     <row r="1383">
       <c r="A1383" t="inlineStr">
@@ -51562,7 +50919,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1383" t="inlineStr"/>
       <c r="E1383" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -51595,7 +50951,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1383" t="inlineStr"/>
     </row>
     <row r="1384">
       <c r="A1384" t="inlineStr">
@@ -51613,7 +50968,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1384" t="inlineStr"/>
       <c r="E1384" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -51646,7 +51000,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1384" t="inlineStr"/>
     </row>
     <row r="1385">
       <c r="A1385" t="inlineStr">
@@ -51664,7 +51017,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1385" t="inlineStr"/>
       <c r="E1385" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -51691,7 +51043,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1385" t="inlineStr"/>
     </row>
     <row r="1386">
       <c r="A1386" t="inlineStr">
@@ -51709,7 +51060,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1386" t="inlineStr"/>
       <c r="E1386" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -51736,7 +51086,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1386" t="inlineStr"/>
     </row>
     <row r="1387">
       <c r="A1387" t="inlineStr">
@@ -51754,7 +51103,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1387" t="inlineStr"/>
       <c r="E1387" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -51787,7 +51135,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1387" t="inlineStr"/>
     </row>
     <row r="1388">
       <c r="A1388" t="inlineStr">
@@ -51805,7 +51152,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1388" t="inlineStr"/>
       <c r="E1388" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -51838,7 +51184,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1388" t="inlineStr"/>
     </row>
     <row r="1389">
       <c r="A1389" t="inlineStr">
@@ -51856,7 +51201,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1389" t="inlineStr"/>
       <c r="E1389" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -51889,7 +51233,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1389" t="inlineStr"/>
     </row>
     <row r="1390">
       <c r="A1390" t="inlineStr">
@@ -51907,7 +51250,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1390" t="inlineStr"/>
       <c r="E1390" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -51934,7 +51276,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1390" t="inlineStr"/>
     </row>
     <row r="1391">
       <c r="A1391" t="inlineStr">
@@ -51952,7 +51293,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1391" t="inlineStr"/>
       <c r="E1391" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -51979,7 +51319,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1391" t="inlineStr"/>
     </row>
     <row r="1392">
       <c r="A1392" t="inlineStr">
@@ -51997,7 +51336,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1392" t="inlineStr"/>
       <c r="E1392" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -52030,7 +51368,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1392" t="inlineStr"/>
     </row>
     <row r="1393">
       <c r="A1393" t="inlineStr">
@@ -52048,7 +51385,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1393" t="inlineStr"/>
       <c r="E1393" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -52075,7 +51411,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1393" t="inlineStr"/>
     </row>
     <row r="1394">
       <c r="A1394" t="inlineStr">
@@ -52093,7 +51428,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1394" t="inlineStr"/>
       <c r="E1394" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -52120,7 +51454,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1394" t="inlineStr"/>
     </row>
     <row r="1395">
       <c r="A1395" t="inlineStr">
@@ -52138,7 +51471,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1395" t="inlineStr"/>
       <c r="E1395" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -52171,7 +51503,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1395" t="inlineStr"/>
     </row>
     <row r="1396">
       <c r="A1396" t="inlineStr">
@@ -52189,7 +51520,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1396" t="inlineStr"/>
       <c r="E1396" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -52222,7 +51552,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1396" t="inlineStr"/>
     </row>
     <row r="1397">
       <c r="A1397" t="inlineStr">
@@ -52240,7 +51569,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1397" t="inlineStr"/>
       <c r="E1397" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -52267,7 +51595,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1397" t="inlineStr"/>
     </row>
     <row r="1398">
       <c r="A1398" t="inlineStr">
@@ -52285,7 +51612,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1398" t="inlineStr"/>
       <c r="E1398" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -52318,7 +51644,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1398" t="inlineStr"/>
     </row>
     <row r="1399">
       <c r="A1399" t="inlineStr">
@@ -52336,7 +51661,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1399" t="inlineStr"/>
       <c r="E1399" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -52369,7 +51693,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1399" t="inlineStr"/>
     </row>
     <row r="1400">
       <c r="A1400" t="inlineStr">
@@ -52387,7 +51710,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1400" t="inlineStr"/>
       <c r="E1400" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -52420,7 +51742,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1400" t="inlineStr"/>
     </row>
     <row r="1401">
       <c r="A1401" t="inlineStr">
@@ -52438,7 +51759,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1401" t="inlineStr"/>
       <c r="E1401" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -52468,7 +51788,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1401" t="inlineStr"/>
     </row>
     <row r="1402">
       <c r="A1402" t="inlineStr">
@@ -52486,7 +51805,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1402" t="inlineStr"/>
       <c r="E1402" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -52519,7 +51837,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1402" t="inlineStr"/>
     </row>
     <row r="1403">
       <c r="A1403" t="inlineStr">
@@ -52537,7 +51854,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1403" t="inlineStr"/>
       <c r="E1403" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -52570,7 +51886,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1403" t="inlineStr"/>
     </row>
     <row r="1404">
       <c r="A1404" t="inlineStr">
@@ -52588,7 +51903,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1404" t="inlineStr"/>
       <c r="E1404" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -52615,7 +51929,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1404" t="inlineStr"/>
     </row>
     <row r="1405">
       <c r="A1405" t="inlineStr">
@@ -52633,7 +51946,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1405" t="inlineStr"/>
       <c r="E1405" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -52666,7 +51978,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1405" t="inlineStr"/>
     </row>
     <row r="1406">
       <c r="A1406" t="inlineStr">
@@ -52684,7 +51995,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1406" t="inlineStr"/>
       <c r="E1406" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -52711,7 +52021,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1406" t="inlineStr"/>
     </row>
     <row r="1407">
       <c r="A1407" t="inlineStr">
@@ -52729,7 +52038,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1407" t="inlineStr"/>
       <c r="E1407" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -52762,7 +52070,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1407" t="inlineStr"/>
     </row>
     <row r="1408">
       <c r="A1408" t="inlineStr">
@@ -52780,7 +52087,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1408" t="inlineStr"/>
       <c r="E1408" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -52813,7 +52119,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1408" t="inlineStr"/>
     </row>
     <row r="1409">
       <c r="A1409" t="inlineStr">
@@ -52831,7 +52136,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1409" t="inlineStr"/>
       <c r="E1409" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -52858,7 +52162,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1409" t="inlineStr"/>
     </row>
     <row r="1410">
       <c r="A1410" t="inlineStr">
@@ -52876,7 +52179,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1410" t="inlineStr"/>
       <c r="E1410" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -52903,7 +52205,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1410" t="inlineStr"/>
     </row>
     <row r="1411">
       <c r="A1411" t="inlineStr">
@@ -52921,7 +52222,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1411" t="inlineStr"/>
       <c r="E1411" t="inlineStr">
         <is>
           <t>Sobrado</t>
@@ -52954,7 +52254,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1411" t="inlineStr"/>
     </row>
     <row r="1412">
       <c r="A1412" t="inlineStr">
@@ -52972,7 +52271,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1412" t="inlineStr"/>
       <c r="E1412" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -53005,7 +52303,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1412" t="inlineStr"/>
     </row>
     <row r="1413">
       <c r="A1413" t="inlineStr">
@@ -53023,7 +52320,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1413" t="inlineStr"/>
       <c r="E1413" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -53056,7 +52352,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1413" t="inlineStr"/>
     </row>
     <row r="1414">
       <c r="A1414" t="inlineStr">
@@ -53074,7 +52369,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1414" t="inlineStr"/>
       <c r="E1414" t="inlineStr">
         <is>
           <t>Prédio Comercial</t>
@@ -53101,7 +52395,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1414" t="inlineStr"/>
     </row>
     <row r="1415">
       <c r="A1415" t="inlineStr">
@@ -53119,7 +52412,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1415" t="inlineStr"/>
       <c r="E1415" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -53146,7 +52438,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1415" t="inlineStr"/>
     </row>
     <row r="1416">
       <c r="A1416" t="inlineStr">
@@ -53164,7 +52455,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1416" t="inlineStr"/>
       <c r="E1416" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -53197,7 +52487,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1416" t="inlineStr"/>
     </row>
     <row r="1417">
       <c r="A1417" t="inlineStr">
@@ -53215,7 +52504,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1417" t="inlineStr"/>
       <c r="E1417" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -53248,7 +52536,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1417" t="inlineStr"/>
     </row>
     <row r="1418">
       <c r="A1418" t="inlineStr">
@@ -53266,7 +52553,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1418" t="inlineStr"/>
       <c r="E1418" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -53299,7 +52585,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1418" t="inlineStr"/>
     </row>
     <row r="1419">
       <c r="A1419" t="inlineStr">
@@ -53317,7 +52602,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1419" t="inlineStr"/>
       <c r="E1419" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -53350,7 +52634,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1419" t="inlineStr"/>
     </row>
     <row r="1420">
       <c r="A1420" t="inlineStr">
@@ -53368,7 +52651,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1420" t="inlineStr"/>
       <c r="E1420" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -53395,7 +52677,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1420" t="inlineStr"/>
     </row>
     <row r="1421">
       <c r="A1421" t="inlineStr">
@@ -53413,7 +52694,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1421" t="inlineStr"/>
       <c r="E1421" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -53446,7 +52726,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1421" t="inlineStr"/>
     </row>
     <row r="1422">
       <c r="A1422" t="inlineStr">
@@ -53464,7 +52743,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1422" t="inlineStr"/>
       <c r="E1422" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -53497,7 +52775,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1422" t="inlineStr"/>
     </row>
     <row r="1423">
       <c r="A1423" t="inlineStr">
@@ -53515,7 +52792,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1423" t="inlineStr"/>
       <c r="E1423" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -53548,7 +52824,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1423" t="inlineStr"/>
     </row>
     <row r="1424">
       <c r="A1424" t="inlineStr">
@@ -53566,7 +52841,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1424" t="inlineStr"/>
       <c r="E1424" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -53599,7 +52873,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1424" t="inlineStr"/>
     </row>
     <row r="1425">
       <c r="A1425" t="inlineStr">
@@ -53617,7 +52890,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1425" t="inlineStr"/>
       <c r="E1425" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -53650,7 +52922,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1425" t="inlineStr"/>
     </row>
     <row r="1426">
       <c r="A1426" t="inlineStr">
@@ -53668,7 +52939,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1426" t="inlineStr"/>
       <c r="E1426" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -53695,7 +52965,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1426" t="inlineStr"/>
     </row>
     <row r="1427">
       <c r="A1427" t="inlineStr">
@@ -53713,7 +52982,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1427" t="inlineStr"/>
       <c r="E1427" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -53740,7 +53008,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1427" t="inlineStr"/>
     </row>
     <row r="1428">
       <c r="A1428" t="inlineStr">
@@ -53758,7 +53025,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1428" t="inlineStr"/>
       <c r="E1428" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -53791,7 +53057,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1428" t="inlineStr"/>
     </row>
     <row r="1429">
       <c r="A1429" t="inlineStr">
@@ -53809,7 +53074,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1429" t="inlineStr"/>
       <c r="E1429" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -53842,7 +53106,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1429" t="inlineStr"/>
     </row>
     <row r="1430">
       <c r="A1430" t="inlineStr">
@@ -53860,7 +53123,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1430" t="inlineStr"/>
       <c r="E1430" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -53887,7 +53149,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1430" t="inlineStr"/>
     </row>
     <row r="1431">
       <c r="A1431" t="inlineStr">
@@ -53905,7 +53166,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1431" t="inlineStr"/>
       <c r="E1431" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -53938,7 +53198,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1431" t="inlineStr"/>
     </row>
     <row r="1432">
       <c r="A1432" t="inlineStr">
@@ -53956,7 +53215,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1432" t="inlineStr"/>
       <c r="E1432" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -53983,7 +53241,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1432" t="inlineStr"/>
     </row>
     <row r="1433">
       <c r="A1433" t="inlineStr">
@@ -54001,7 +53258,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1433" t="inlineStr"/>
       <c r="E1433" t="inlineStr">
         <is>
           <t>Prédio Comercial</t>
@@ -54028,7 +53284,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1433" t="inlineStr"/>
     </row>
     <row r="1434">
       <c r="A1434" t="inlineStr">
@@ -54046,7 +53301,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1434" t="inlineStr"/>
       <c r="E1434" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -54079,7 +53333,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1434" t="inlineStr"/>
     </row>
     <row r="1435">
       <c r="A1435" t="inlineStr">
@@ -54097,7 +53350,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1435" t="inlineStr"/>
       <c r="E1435" t="inlineStr">
         <is>
           <t>Sobrado</t>
@@ -54130,7 +53382,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1435" t="inlineStr"/>
     </row>
     <row r="1436">
       <c r="A1436" t="inlineStr">
@@ -54148,7 +53399,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1436" t="inlineStr"/>
       <c r="E1436" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -54181,7 +53431,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1436" t="inlineStr"/>
     </row>
     <row r="1437">
       <c r="A1437" t="inlineStr">
@@ -54199,7 +53448,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1437" t="inlineStr"/>
       <c r="E1437" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -54226,7 +53474,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1437" t="inlineStr"/>
     </row>
     <row r="1438">
       <c r="A1438" t="inlineStr">
@@ -54244,7 +53491,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1438" t="inlineStr"/>
       <c r="E1438" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -54277,7 +53523,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1438" t="inlineStr"/>
     </row>
     <row r="1439">
       <c r="A1439" t="inlineStr">
@@ -54295,7 +53540,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1439" t="inlineStr"/>
       <c r="E1439" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -54322,7 +53566,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1439" t="inlineStr"/>
     </row>
     <row r="1440">
       <c r="A1440" t="inlineStr">
@@ -54340,7 +53583,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1440" t="inlineStr"/>
       <c r="E1440" t="inlineStr">
         <is>
           <t>Sobrado</t>
@@ -54373,7 +53615,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1440" t="inlineStr"/>
     </row>
     <row r="1441">
       <c r="A1441" t="inlineStr">
@@ -54391,7 +53632,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1441" t="inlineStr"/>
       <c r="E1441" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -54418,7 +53658,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1441" t="inlineStr"/>
     </row>
     <row r="1442">
       <c r="A1442" t="inlineStr">
@@ -54436,7 +53675,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1442" t="inlineStr"/>
       <c r="E1442" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -54469,7 +53707,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1442" t="inlineStr"/>
     </row>
     <row r="1443">
       <c r="A1443" t="inlineStr">
@@ -54487,7 +53724,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1443" t="inlineStr"/>
       <c r="E1443" t="inlineStr">
         <is>
           <t>Prédio Comercial</t>
@@ -54517,7 +53753,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1443" t="inlineStr"/>
     </row>
     <row r="1444">
       <c r="A1444" t="inlineStr">
@@ -54535,7 +53770,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1444" t="inlineStr"/>
       <c r="E1444" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -54562,7 +53796,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1444" t="inlineStr"/>
     </row>
     <row r="1445">
       <c r="A1445" t="inlineStr">
@@ -54580,7 +53813,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1445" t="inlineStr"/>
       <c r="E1445" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -54613,7 +53845,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1445" t="inlineStr"/>
     </row>
     <row r="1446">
       <c r="A1446" t="inlineStr">
@@ -54631,7 +53862,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1446" t="inlineStr"/>
       <c r="E1446" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -54664,7 +53894,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1446" t="inlineStr"/>
     </row>
     <row r="1447">
       <c r="A1447" t="inlineStr">
@@ -54682,7 +53911,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1447" t="inlineStr"/>
       <c r="E1447" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -54709,7 +53937,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1447" t="inlineStr"/>
     </row>
     <row r="1448">
       <c r="A1448" t="inlineStr">
@@ -54727,7 +53954,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1448" t="inlineStr"/>
       <c r="E1448" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -54760,7 +53986,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1448" t="inlineStr"/>
     </row>
     <row r="1449">
       <c r="A1449" t="inlineStr">
@@ -54778,7 +54003,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1449" t="inlineStr"/>
       <c r="E1449" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -54811,7 +54035,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1449" t="inlineStr"/>
     </row>
     <row r="1450">
       <c r="A1450" t="inlineStr">
@@ -54829,7 +54052,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1450" t="inlineStr"/>
       <c r="E1450" t="inlineStr">
         <is>
           <t>Sobrado</t>
@@ -54859,7 +54081,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1450" t="inlineStr"/>
     </row>
     <row r="1451">
       <c r="A1451" t="inlineStr">
@@ -54877,7 +54098,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1451" t="inlineStr"/>
       <c r="E1451" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -54910,7 +54130,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1451" t="inlineStr"/>
     </row>
     <row r="1452">
       <c r="A1452" t="inlineStr">
@@ -54928,7 +54147,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1452" t="inlineStr"/>
       <c r="E1452" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -54955,7 +54173,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1452" t="inlineStr"/>
     </row>
     <row r="1453">
       <c r="A1453" t="inlineStr">
@@ -54973,7 +54190,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1453" t="inlineStr"/>
       <c r="E1453" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -55006,7 +54222,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1453" t="inlineStr"/>
     </row>
     <row r="1454">
       <c r="A1454" t="inlineStr">
@@ -55024,7 +54239,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1454" t="inlineStr"/>
       <c r="E1454" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -55051,7 +54265,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1454" t="inlineStr"/>
     </row>
     <row r="1455">
       <c r="A1455" t="inlineStr">
@@ -55069,7 +54282,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1455" t="inlineStr"/>
       <c r="E1455" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -55096,7 +54308,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1455" t="inlineStr"/>
     </row>
     <row r="1456">
       <c r="A1456" t="inlineStr">
@@ -55114,13 +54325,11 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1456" t="inlineStr"/>
       <c r="E1456" t="inlineStr">
         <is>
           <t>Galpão</t>
         </is>
       </c>
-      <c r="F1456" t="inlineStr"/>
       <c r="G1456" t="n">
         <v>408</v>
       </c>
@@ -55137,7 +54346,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1456" t="inlineStr"/>
     </row>
     <row r="1457">
       <c r="A1457" t="inlineStr">
@@ -55155,7 +54363,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1457" t="inlineStr"/>
       <c r="E1457" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -55188,7 +54395,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1457" t="inlineStr"/>
     </row>
     <row r="1458">
       <c r="A1458" t="inlineStr">
@@ -55206,7 +54412,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1458" t="inlineStr"/>
       <c r="E1458" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -55239,7 +54444,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1458" t="inlineStr"/>
     </row>
     <row r="1459">
       <c r="A1459" t="inlineStr">
@@ -55257,7 +54461,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1459" t="inlineStr"/>
       <c r="E1459" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -55287,7 +54490,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1459" t="inlineStr"/>
     </row>
     <row r="1460">
       <c r="A1460" t="inlineStr">
@@ -55305,7 +54507,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1460" t="inlineStr"/>
       <c r="E1460" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -55338,7 +54539,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1460" t="inlineStr"/>
     </row>
     <row r="1461">
       <c r="A1461" t="inlineStr">
@@ -55356,7 +54556,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1461" t="inlineStr"/>
       <c r="E1461" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -55383,7 +54582,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1461" t="inlineStr"/>
     </row>
     <row r="1462">
       <c r="A1462" t="inlineStr">
@@ -55401,7 +54599,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1462" t="inlineStr"/>
       <c r="E1462" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -55428,7 +54625,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1462" t="inlineStr"/>
     </row>
     <row r="1463">
       <c r="A1463" t="inlineStr">
@@ -55446,7 +54642,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1463" t="inlineStr"/>
       <c r="E1463" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -55479,7 +54674,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1463" t="inlineStr"/>
     </row>
     <row r="1464">
       <c r="A1464" t="inlineStr">
@@ -55497,7 +54691,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1464" t="inlineStr"/>
       <c r="E1464" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -55530,7 +54723,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1464" t="inlineStr"/>
     </row>
     <row r="1465">
       <c r="A1465" t="inlineStr">
@@ -55548,7 +54740,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1465" t="inlineStr"/>
       <c r="E1465" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -55575,7 +54766,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1465" t="inlineStr"/>
     </row>
     <row r="1466">
       <c r="A1466" t="inlineStr">
@@ -55593,7 +54783,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1466" t="inlineStr"/>
       <c r="E1466" t="inlineStr">
         <is>
           <t>Sobrado</t>
@@ -55626,7 +54815,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1466" t="inlineStr"/>
     </row>
     <row r="1467">
       <c r="A1467" t="inlineStr">
@@ -55644,7 +54832,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1467" t="inlineStr"/>
       <c r="E1467" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -55674,7 +54861,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1467" t="inlineStr"/>
     </row>
     <row r="1468">
       <c r="A1468" t="inlineStr">
@@ -55692,7 +54878,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1468" t="inlineStr"/>
       <c r="E1468" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -55719,7 +54904,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1468" t="inlineStr"/>
     </row>
     <row r="1469">
       <c r="A1469" t="inlineStr">
@@ -55737,7 +54921,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1469" t="inlineStr"/>
       <c r="E1469" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -55764,7 +54947,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1469" t="inlineStr"/>
     </row>
     <row r="1470">
       <c r="A1470" t="inlineStr">
@@ -55782,7 +54964,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1470" t="inlineStr"/>
       <c r="E1470" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -55809,7 +54990,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1470" t="inlineStr"/>
     </row>
     <row r="1471">
       <c r="A1471" t="inlineStr">
@@ -55827,7 +55007,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1471" t="inlineStr"/>
       <c r="E1471" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -55860,7 +55039,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1471" t="inlineStr"/>
     </row>
     <row r="1472">
       <c r="A1472" t="inlineStr">
@@ -55878,7 +55056,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1472" t="inlineStr"/>
       <c r="E1472" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -55911,7 +55088,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1472" t="inlineStr"/>
     </row>
     <row r="1473">
       <c r="A1473" t="inlineStr">
@@ -55929,7 +55105,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1473" t="inlineStr"/>
       <c r="E1473" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -55962,7 +55137,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1473" t="inlineStr"/>
     </row>
     <row r="1474">
       <c r="A1474" t="inlineStr">
@@ -55980,7 +55154,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1474" t="inlineStr"/>
       <c r="E1474" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -56013,7 +55186,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1474" t="inlineStr"/>
     </row>
     <row r="1475">
       <c r="A1475" t="inlineStr">
@@ -56031,7 +55203,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1475" t="inlineStr"/>
       <c r="E1475" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -56058,7 +55229,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1475" t="inlineStr"/>
     </row>
     <row r="1476">
       <c r="A1476" t="inlineStr">
@@ -56076,7 +55246,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1476" t="inlineStr"/>
       <c r="E1476" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -56109,7 +55278,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1476" t="inlineStr"/>
     </row>
     <row r="1477">
       <c r="A1477" t="inlineStr">
@@ -56127,7 +55295,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1477" t="inlineStr"/>
       <c r="E1477" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -56160,7 +55327,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1477" t="inlineStr"/>
     </row>
     <row r="1478">
       <c r="A1478" t="inlineStr">
@@ -56178,7 +55344,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1478" t="inlineStr"/>
       <c r="E1478" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -56211,7 +55376,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1478" t="inlineStr"/>
     </row>
     <row r="1479">
       <c r="A1479" t="inlineStr">
@@ -56229,7 +55393,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1479" t="inlineStr"/>
       <c r="E1479" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -56262,7 +55425,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1479" t="inlineStr"/>
     </row>
     <row r="1480">
       <c r="A1480" t="inlineStr">
@@ -56280,7 +55442,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1480" t="inlineStr"/>
       <c r="E1480" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -56313,7 +55474,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1480" t="inlineStr"/>
     </row>
     <row r="1481">
       <c r="A1481" t="inlineStr">
@@ -56331,7 +55491,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1481" t="inlineStr"/>
       <c r="E1481" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -56358,7 +55517,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1481" t="inlineStr"/>
     </row>
     <row r="1482">
       <c r="A1482" t="inlineStr">
@@ -56376,7 +55534,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1482" t="inlineStr"/>
       <c r="E1482" t="inlineStr">
         <is>
           <t>Prédio Comercial</t>
@@ -56403,7 +55560,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1482" t="inlineStr"/>
     </row>
     <row r="1483">
       <c r="A1483" t="inlineStr">
@@ -56421,7 +55577,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1483" t="inlineStr"/>
       <c r="E1483" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -56454,7 +55609,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1483" t="inlineStr"/>
     </row>
     <row r="1484">
       <c r="A1484" t="inlineStr">
@@ -56472,7 +55626,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1484" t="inlineStr"/>
       <c r="E1484" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -56505,7 +55658,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1484" t="inlineStr"/>
     </row>
     <row r="1485">
       <c r="A1485" t="inlineStr">
@@ -56523,7 +55675,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1485" t="inlineStr"/>
       <c r="E1485" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -56556,7 +55707,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1485" t="inlineStr"/>
     </row>
     <row r="1486">
       <c r="A1486" t="inlineStr">
@@ -56574,7 +55724,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1486" t="inlineStr"/>
       <c r="E1486" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -56607,7 +55756,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1486" t="inlineStr"/>
     </row>
     <row r="1487">
       <c r="A1487" t="inlineStr">
@@ -56625,7 +55773,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1487" t="inlineStr"/>
       <c r="E1487" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -56658,7 +55805,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1487" t="inlineStr"/>
     </row>
     <row r="1488">
       <c r="A1488" t="inlineStr">
@@ -56676,7 +55822,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1488" t="inlineStr"/>
       <c r="E1488" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -56709,7 +55854,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1488" t="inlineStr"/>
     </row>
     <row r="1489">
       <c r="A1489" t="inlineStr">
@@ -56727,7 +55871,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1489" t="inlineStr"/>
       <c r="E1489" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -56760,7 +55903,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1489" t="inlineStr"/>
     </row>
     <row r="1490">
       <c r="A1490" t="inlineStr">
@@ -56778,7 +55920,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1490" t="inlineStr"/>
       <c r="E1490" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -56805,7 +55946,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1490" t="inlineStr"/>
     </row>
     <row r="1491">
       <c r="A1491" t="inlineStr">
@@ -56823,7 +55963,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1491" t="inlineStr"/>
       <c r="E1491" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -56850,7 +55989,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1491" t="inlineStr"/>
     </row>
     <row r="1492">
       <c r="A1492" t="inlineStr">
@@ -56868,7 +56006,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1492" t="inlineStr"/>
       <c r="E1492" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -56895,7 +56032,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1492" t="inlineStr"/>
     </row>
     <row r="1493">
       <c r="A1493" t="inlineStr">
@@ -56913,7 +56049,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1493" t="inlineStr"/>
       <c r="E1493" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -56943,7 +56078,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1493" t="inlineStr"/>
     </row>
     <row r="1494">
       <c r="A1494" t="inlineStr">
@@ -56961,7 +56095,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1494" t="inlineStr"/>
       <c r="E1494" t="inlineStr">
         <is>
           <t>Imóvel Comercial</t>
@@ -56994,7 +56127,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1494" t="inlineStr"/>
     </row>
     <row r="1495">
       <c r="A1495" t="inlineStr">
@@ -57012,7 +56144,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1495" t="inlineStr"/>
       <c r="E1495" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -57045,7 +56176,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1495" t="inlineStr"/>
     </row>
     <row r="1496">
       <c r="A1496" t="inlineStr">
@@ -57063,7 +56193,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1496" t="inlineStr"/>
       <c r="E1496" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -57090,7 +56219,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1496" t="inlineStr"/>
     </row>
     <row r="1497">
       <c r="A1497" t="inlineStr">
@@ -57108,7 +56236,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1497" t="inlineStr"/>
       <c r="E1497" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -57135,7 +56262,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1497" t="inlineStr"/>
     </row>
     <row r="1498">
       <c r="A1498" t="inlineStr">
@@ -57153,7 +56279,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1498" t="inlineStr"/>
       <c r="E1498" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -57186,7 +56311,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1498" t="inlineStr"/>
     </row>
     <row r="1499">
       <c r="A1499" t="inlineStr">
@@ -57204,7 +56328,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1499" t="inlineStr"/>
       <c r="E1499" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -57231,7 +56354,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1499" t="inlineStr"/>
     </row>
     <row r="1500">
       <c r="A1500" t="inlineStr">
@@ -57249,7 +56371,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1500" t="inlineStr"/>
       <c r="E1500" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -57282,7 +56403,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1500" t="inlineStr"/>
     </row>
     <row r="1501">
       <c r="A1501" t="inlineStr">
@@ -57300,7 +56420,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1501" t="inlineStr"/>
       <c r="E1501" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -57333,7 +56452,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1501" t="inlineStr"/>
     </row>
     <row r="1502">
       <c r="A1502" t="inlineStr">
@@ -57351,7 +56469,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1502" t="inlineStr"/>
       <c r="E1502" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -57384,7 +56501,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1502" t="inlineStr"/>
     </row>
     <row r="1503">
       <c r="A1503" t="inlineStr">
@@ -57402,7 +56518,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1503" t="inlineStr"/>
       <c r="E1503" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -57429,7 +56544,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1503" t="inlineStr"/>
     </row>
     <row r="1504">
       <c r="A1504" t="inlineStr">
@@ -57447,7 +56561,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1504" t="inlineStr"/>
       <c r="E1504" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -57480,7 +56593,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1504" t="inlineStr"/>
     </row>
     <row r="1505">
       <c r="A1505" t="inlineStr">
@@ -57498,7 +56610,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1505" t="inlineStr"/>
       <c r="E1505" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -57531,7 +56642,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1505" t="inlineStr"/>
     </row>
     <row r="1506">
       <c r="A1506" t="inlineStr">
@@ -57549,7 +56659,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1506" t="inlineStr"/>
       <c r="E1506" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -57582,7 +56691,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1506" t="inlineStr"/>
     </row>
     <row r="1507">
       <c r="A1507" t="inlineStr">
@@ -57600,7 +56708,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1507" t="inlineStr"/>
       <c r="E1507" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -57627,7 +56734,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1507" t="inlineStr"/>
     </row>
     <row r="1508">
       <c r="A1508" t="inlineStr">
@@ -57645,7 +56751,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1508" t="inlineStr"/>
       <c r="E1508" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -57678,7 +56783,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1508" t="inlineStr"/>
     </row>
     <row r="1509">
       <c r="A1509" t="inlineStr">
@@ -57696,7 +56800,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1509" t="inlineStr"/>
       <c r="E1509" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -57729,7 +56832,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1509" t="inlineStr"/>
     </row>
     <row r="1510">
       <c r="A1510" t="inlineStr">
@@ -57747,7 +56849,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1510" t="inlineStr"/>
       <c r="E1510" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -57774,7 +56875,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1510" t="inlineStr"/>
     </row>
     <row r="1511">
       <c r="A1511" t="inlineStr">
@@ -57792,7 +56892,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1511" t="inlineStr"/>
       <c r="E1511" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -57825,7 +56924,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1511" t="inlineStr"/>
     </row>
     <row r="1512">
       <c r="A1512" t="inlineStr">
@@ -57843,7 +56941,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1512" t="inlineStr"/>
       <c r="E1512" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -57870,7 +56967,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1512" t="inlineStr"/>
     </row>
     <row r="1513">
       <c r="A1513" t="inlineStr">
@@ -57888,7 +56984,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1513" t="inlineStr"/>
       <c r="E1513" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -57921,7 +57016,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1513" t="inlineStr"/>
     </row>
     <row r="1514">
       <c r="A1514" t="inlineStr">
@@ -57939,7 +57033,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1514" t="inlineStr"/>
       <c r="E1514" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -57972,7 +57065,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1514" t="inlineStr"/>
     </row>
     <row r="1515">
       <c r="A1515" t="inlineStr">
@@ -57990,7 +57082,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1515" t="inlineStr"/>
       <c r="E1515" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -58023,7 +57114,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1515" t="inlineStr"/>
     </row>
     <row r="1516">
       <c r="A1516" t="inlineStr">
@@ -58041,7 +57131,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1516" t="inlineStr"/>
       <c r="E1516" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -58068,7 +57157,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1516" t="inlineStr"/>
     </row>
     <row r="1517">
       <c r="A1517" t="inlineStr">
@@ -58086,7 +57174,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1517" t="inlineStr"/>
       <c r="E1517" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -58119,7 +57206,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1517" t="inlineStr"/>
     </row>
     <row r="1518">
       <c r="A1518" t="inlineStr">
@@ -58137,7 +57223,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1518" t="inlineStr"/>
       <c r="E1518" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -58164,7 +57249,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1518" t="inlineStr"/>
     </row>
     <row r="1519">
       <c r="A1519" t="inlineStr">
@@ -58182,7 +57266,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1519" t="inlineStr"/>
       <c r="E1519" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -58209,7 +57292,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1519" t="inlineStr"/>
     </row>
     <row r="1520">
       <c r="A1520" t="inlineStr">
@@ -58227,7 +57309,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1520" t="inlineStr"/>
       <c r="E1520" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -58254,7 +57335,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1520" t="inlineStr"/>
     </row>
     <row r="1521">
       <c r="A1521" t="inlineStr">
@@ -58272,7 +57352,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1521" t="inlineStr"/>
       <c r="E1521" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -58299,7 +57378,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1521" t="inlineStr"/>
     </row>
     <row r="1522">
       <c r="A1522" t="inlineStr">
@@ -58317,7 +57395,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1522" t="inlineStr"/>
       <c r="E1522" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -58350,7 +57427,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1522" t="inlineStr"/>
     </row>
     <row r="1523">
       <c r="A1523" t="inlineStr">
@@ -58368,7 +57444,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1523" t="inlineStr"/>
       <c r="E1523" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -58401,7 +57476,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1523" t="inlineStr"/>
     </row>
     <row r="1524">
       <c r="A1524" t="inlineStr">
@@ -58419,7 +57493,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1524" t="inlineStr"/>
       <c r="E1524" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -58446,7 +57519,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1524" t="inlineStr"/>
     </row>
     <row r="1525">
       <c r="A1525" t="inlineStr">
@@ -58464,7 +57536,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1525" t="inlineStr"/>
       <c r="E1525" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -58497,7 +57568,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1525" t="inlineStr"/>
     </row>
     <row r="1526">
       <c r="A1526" t="inlineStr">
@@ -58515,7 +57585,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1526" t="inlineStr"/>
       <c r="E1526" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -58542,7 +57611,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1526" t="inlineStr"/>
     </row>
     <row r="1527">
       <c r="A1527" t="inlineStr">
@@ -58560,7 +57628,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1527" t="inlineStr"/>
       <c r="E1527" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -58593,7 +57660,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1527" t="inlineStr"/>
     </row>
     <row r="1528">
       <c r="A1528" t="inlineStr">
@@ -58611,7 +57677,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1528" t="inlineStr"/>
       <c r="E1528" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -58644,7 +57709,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1528" t="inlineStr"/>
     </row>
     <row r="1529">
       <c r="A1529" t="inlineStr">
@@ -58662,7 +57726,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1529" t="inlineStr"/>
       <c r="E1529" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -58695,7 +57758,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1529" t="inlineStr"/>
     </row>
     <row r="1530">
       <c r="A1530" t="inlineStr">
@@ -58713,7 +57775,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1530" t="inlineStr"/>
       <c r="E1530" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -58746,7 +57807,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1530" t="inlineStr"/>
     </row>
     <row r="1531">
       <c r="A1531" t="inlineStr">
@@ -58764,7 +57824,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1531" t="inlineStr"/>
       <c r="E1531" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -58791,7 +57850,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1531" t="inlineStr"/>
     </row>
     <row r="1532">
       <c r="A1532" t="inlineStr">
@@ -58809,7 +57867,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1532" t="inlineStr"/>
       <c r="E1532" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -58836,7 +57893,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1532" t="inlineStr"/>
     </row>
     <row r="1533">
       <c r="A1533" t="inlineStr">
@@ -58854,7 +57910,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1533" t="inlineStr"/>
       <c r="E1533" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -58884,7 +57939,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1533" t="inlineStr"/>
     </row>
     <row r="1534">
       <c r="A1534" t="inlineStr">
@@ -58902,7 +57956,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1534" t="inlineStr"/>
       <c r="E1534" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -58935,7 +57988,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1534" t="inlineStr"/>
     </row>
     <row r="1535">
       <c r="A1535" t="inlineStr">
@@ -58953,7 +58005,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1535" t="inlineStr"/>
       <c r="E1535" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -58986,7 +58037,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1535" t="inlineStr"/>
     </row>
     <row r="1536">
       <c r="A1536" t="inlineStr">
@@ -59004,7 +58054,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1536" t="inlineStr"/>
       <c r="E1536" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -59037,7 +58086,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1536" t="inlineStr"/>
     </row>
     <row r="1537">
       <c r="A1537" t="inlineStr">
@@ -59055,7 +58103,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1537" t="inlineStr"/>
       <c r="E1537" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -59088,7 +58135,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1537" t="inlineStr"/>
     </row>
     <row r="1538">
       <c r="A1538" t="inlineStr">
@@ -59106,7 +58152,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1538" t="inlineStr"/>
       <c r="E1538" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -59133,7 +58178,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1538" t="inlineStr"/>
     </row>
     <row r="1539">
       <c r="A1539" t="inlineStr">
@@ -59151,7 +58195,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1539" t="inlineStr"/>
       <c r="E1539" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -59184,7 +58227,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1539" t="inlineStr"/>
     </row>
     <row r="1540">
       <c r="A1540" t="inlineStr">
@@ -59202,7 +58244,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1540" t="inlineStr"/>
       <c r="E1540" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -59229,7 +58270,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1540" t="inlineStr"/>
     </row>
     <row r="1541">
       <c r="A1541" t="inlineStr">
@@ -59247,7 +58287,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1541" t="inlineStr"/>
       <c r="E1541" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -59274,7 +58313,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1541" t="inlineStr"/>
     </row>
     <row r="1542">
       <c r="A1542" t="inlineStr">
@@ -59292,7 +58330,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1542" t="inlineStr"/>
       <c r="E1542" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -59325,7 +58362,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1542" t="inlineStr"/>
     </row>
     <row r="1543">
       <c r="A1543" t="inlineStr">
@@ -59343,7 +58379,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1543" t="inlineStr"/>
       <c r="E1543" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -59370,7 +58405,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1543" t="inlineStr"/>
     </row>
     <row r="1544">
       <c r="A1544" t="inlineStr">
@@ -59388,7 +58422,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1544" t="inlineStr"/>
       <c r="E1544" t="inlineStr">
         <is>
           <t>Casa</t>
@@ -59421,7 +58454,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1544" t="inlineStr"/>
     </row>
     <row r="1545">
       <c r="A1545" t="inlineStr">
@@ -59439,7 +58471,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1545" t="inlineStr"/>
       <c r="E1545" t="inlineStr">
         <is>
           <t>Terreno</t>
@@ -59466,7 +58497,6 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1545" t="inlineStr"/>
     </row>
     <row r="1546">
       <c r="A1546" t="inlineStr">
@@ -59484,7 +58514,6 @@
           <t>VivaReal</t>
         </is>
       </c>
-      <c r="D1546" t="inlineStr"/>
       <c r="E1546" t="inlineStr">
         <is>
           <t>Apartamento</t>
@@ -59517,7 +58546,1203 @@
           <t>Venda</t>
         </is>
       </c>
-      <c r="N1546" t="inlineStr"/>
+    </row>
+    <row r="1547">
+      <c r="A1547" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1547" t="inlineStr">
+        <is>
+          <t>vivareal.com.br</t>
+        </is>
+      </c>
+      <c r="C1547" t="inlineStr">
+        <is>
+          <t>VivaReal</t>
+        </is>
+      </c>
+      <c r="D1547" t="inlineStr"/>
+      <c r="E1547" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="F1547" t="inlineStr">
+        <is>
+          <t>Jardim Los Angeles · Rua Califórnia</t>
+        </is>
+      </c>
+      <c r="G1547" t="n">
+        <v>112</v>
+      </c>
+      <c r="H1547" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1547" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1547" t="n">
+        <v>550000</v>
+      </c>
+      <c r="L1547" t="inlineStr">
+        <is>
+          <t>VivaReal | id:2895677303</t>
+        </is>
+      </c>
+      <c r="M1547" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="N1547" t="inlineStr"/>
+    </row>
+    <row r="1548">
+      <c r="A1548" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1548" t="inlineStr">
+        <is>
+          <t>vivareal.com.br</t>
+        </is>
+      </c>
+      <c r="C1548" t="inlineStr">
+        <is>
+          <t>VivaReal</t>
+        </is>
+      </c>
+      <c r="D1548" t="inlineStr"/>
+      <c r="E1548" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="F1548" t="inlineStr">
+        <is>
+          <t>Zona 08 · Avenida Guedner</t>
+        </is>
+      </c>
+      <c r="G1548" t="n">
+        <v>87</v>
+      </c>
+      <c r="H1548" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1548" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1548" t="n">
+        <v>590000</v>
+      </c>
+      <c r="L1548" t="inlineStr">
+        <is>
+          <t>VivaReal | id:2895106397</t>
+        </is>
+      </c>
+      <c r="M1548" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="N1548" t="inlineStr"/>
+    </row>
+    <row r="1549">
+      <c r="A1549" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1549" t="inlineStr">
+        <is>
+          <t>vivareal.com.br</t>
+        </is>
+      </c>
+      <c r="C1549" t="inlineStr">
+        <is>
+          <t>VivaReal</t>
+        </is>
+      </c>
+      <c r="D1549" t="inlineStr"/>
+      <c r="E1549" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="F1549" t="inlineStr">
+        <is>
+          <t>Jardim Três Lagoas · Rua Henri Jean Viana Júnior</t>
+        </is>
+      </c>
+      <c r="G1549" t="n">
+        <v>123</v>
+      </c>
+      <c r="H1549" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1549" t="n">
+        <v>3</v>
+      </c>
+      <c r="K1549" t="n">
+        <v>530000</v>
+      </c>
+      <c r="L1549" t="inlineStr">
+        <is>
+          <t>VivaReal | id:2760096627</t>
+        </is>
+      </c>
+      <c r="M1549" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="N1549" t="inlineStr"/>
+    </row>
+    <row r="1550">
+      <c r="A1550" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1550" t="inlineStr">
+        <is>
+          <t>vivareal.com.br</t>
+        </is>
+      </c>
+      <c r="C1550" t="inlineStr">
+        <is>
+          <t>VivaReal</t>
+        </is>
+      </c>
+      <c r="D1550" t="inlineStr"/>
+      <c r="E1550" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="F1550" t="inlineStr">
+        <is>
+          <t>Jardim América · Rua Sérgio Bittencourt</t>
+        </is>
+      </c>
+      <c r="G1550" t="n">
+        <v>151</v>
+      </c>
+      <c r="H1550" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1550" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1550" t="n">
+        <v>580000</v>
+      </c>
+      <c r="L1550" t="inlineStr">
+        <is>
+          <t>VivaReal | id:2825362231</t>
+        </is>
+      </c>
+      <c r="M1550" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="N1550" t="inlineStr"/>
+    </row>
+    <row r="1551">
+      <c r="A1551" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1551" t="inlineStr">
+        <is>
+          <t>vivareal.com.br</t>
+        </is>
+      </c>
+      <c r="C1551" t="inlineStr">
+        <is>
+          <t>VivaReal</t>
+        </is>
+      </c>
+      <c r="D1551" t="inlineStr"/>
+      <c r="E1551" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="F1551" t="inlineStr">
+        <is>
+          <t>Jardim Licce · Rua Nestor Narcizo de Souza</t>
+        </is>
+      </c>
+      <c r="G1551" t="n">
+        <v>99</v>
+      </c>
+      <c r="H1551" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1551" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1551" t="n">
+        <v>510000</v>
+      </c>
+      <c r="L1551" t="inlineStr">
+        <is>
+          <t>VivaReal | id:2895586577</t>
+        </is>
+      </c>
+      <c r="M1551" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="N1551" t="inlineStr"/>
+    </row>
+    <row r="1552">
+      <c r="A1552" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1552" t="inlineStr">
+        <is>
+          <t>vivareal.com.br</t>
+        </is>
+      </c>
+      <c r="C1552" t="inlineStr">
+        <is>
+          <t>VivaReal</t>
+        </is>
+      </c>
+      <c r="D1552" t="inlineStr"/>
+      <c r="E1552" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="F1552" t="inlineStr">
+        <is>
+          <t>Jardim América · Avenida das Indústrias</t>
+        </is>
+      </c>
+      <c r="G1552" t="n">
+        <v>47</v>
+      </c>
+      <c r="H1552" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1552" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1552" t="n">
+        <v>320000</v>
+      </c>
+      <c r="L1552" t="inlineStr">
+        <is>
+          <t>VivaReal | id:2867310960</t>
+        </is>
+      </c>
+      <c r="M1552" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="N1552" t="inlineStr"/>
+    </row>
+    <row r="1553">
+      <c r="A1553" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1553" t="inlineStr">
+        <is>
+          <t>vivareal.com.br</t>
+        </is>
+      </c>
+      <c r="C1553" t="inlineStr">
+        <is>
+          <t>VivaReal</t>
+        </is>
+      </c>
+      <c r="D1553" t="inlineStr"/>
+      <c r="E1553" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="F1553" t="inlineStr">
+        <is>
+          <t>Jardim dos Pássaros · Rua Guaratinga</t>
+        </is>
+      </c>
+      <c r="G1553" t="n">
+        <v>105</v>
+      </c>
+      <c r="H1553" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1553" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1553" t="n">
+        <v>529900</v>
+      </c>
+      <c r="L1553" t="inlineStr">
+        <is>
+          <t>VivaReal | id:2873879921</t>
+        </is>
+      </c>
+      <c r="M1553" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="N1553" t="inlineStr"/>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1554" t="inlineStr">
+        <is>
+          <t>vivareal.com.br</t>
+        </is>
+      </c>
+      <c r="C1554" t="inlineStr">
+        <is>
+          <t>VivaReal</t>
+        </is>
+      </c>
+      <c r="D1554" t="inlineStr"/>
+      <c r="E1554" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="F1554" t="inlineStr">
+        <is>
+          <t>Jardim Diamante · Rua Pioneiro Olinto Mariani</t>
+        </is>
+      </c>
+      <c r="G1554" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1554" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1554" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1554" t="n">
+        <v>420000</v>
+      </c>
+      <c r="L1554" t="inlineStr">
+        <is>
+          <t>VivaReal | id:2826496652</t>
+        </is>
+      </c>
+      <c r="M1554" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="N1554" t="inlineStr"/>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1555" t="inlineStr">
+        <is>
+          <t>vivareal.com.br</t>
+        </is>
+      </c>
+      <c r="C1555" t="inlineStr">
+        <is>
+          <t>VivaReal</t>
+        </is>
+      </c>
+      <c r="D1555" t="inlineStr"/>
+      <c r="E1555" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="F1555" t="inlineStr">
+        <is>
+          <t>Jardim Santa Helena · Rua Brilhante</t>
+        </is>
+      </c>
+      <c r="G1555" t="n">
+        <v>142</v>
+      </c>
+      <c r="H1555" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1555" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1555" t="n">
+        <v>790000</v>
+      </c>
+      <c r="L1555" t="inlineStr">
+        <is>
+          <t>VivaReal | id:2891150691</t>
+        </is>
+      </c>
+      <c r="M1555" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="N1555" t="inlineStr"/>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1556" t="inlineStr">
+        <is>
+          <t>vivareal.com.br</t>
+        </is>
+      </c>
+      <c r="C1556" t="inlineStr">
+        <is>
+          <t>VivaReal</t>
+        </is>
+      </c>
+      <c r="D1556" t="inlineStr"/>
+      <c r="E1556" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="F1556" t="inlineStr">
+        <is>
+          <t>Parque Residencial Cidade Nova · Rua João Luiz Dias</t>
+        </is>
+      </c>
+      <c r="G1556" t="n">
+        <v>54</v>
+      </c>
+      <c r="H1556" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1556" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1556" t="n">
+        <v>225000</v>
+      </c>
+      <c r="L1556" t="inlineStr">
+        <is>
+          <t>VivaReal | id:2871783492</t>
+        </is>
+      </c>
+      <c r="M1556" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="N1556" t="inlineStr"/>
+    </row>
+    <row r="1557">
+      <c r="A1557" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1557" t="inlineStr">
+        <is>
+          <t>vivareal.com.br</t>
+        </is>
+      </c>
+      <c r="C1557" t="inlineStr">
+        <is>
+          <t>VivaReal</t>
+        </is>
+      </c>
+      <c r="D1557" t="inlineStr"/>
+      <c r="E1557" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="F1557" t="inlineStr">
+        <is>
+          <t>Conjunto Habitacional Karina · Rua Vitório Sambatti</t>
+        </is>
+      </c>
+      <c r="G1557" t="n">
+        <v>76</v>
+      </c>
+      <c r="H1557" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1557" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1557" t="n">
+        <v>390000</v>
+      </c>
+      <c r="L1557" t="inlineStr">
+        <is>
+          <t>VivaReal | id:2893784124</t>
+        </is>
+      </c>
+      <c r="M1557" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="N1557" t="inlineStr"/>
+    </row>
+    <row r="1558">
+      <c r="A1558" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1558" t="inlineStr">
+        <is>
+          <t>vivareal.com.br</t>
+        </is>
+      </c>
+      <c r="C1558" t="inlineStr">
+        <is>
+          <t>VivaReal</t>
+        </is>
+      </c>
+      <c r="D1558" t="inlineStr"/>
+      <c r="E1558" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="F1558" t="inlineStr">
+        <is>
+          <t>Jardim Aclimação · Rua Ernesto Mariucci</t>
+        </is>
+      </c>
+      <c r="G1558" t="n">
+        <v>54</v>
+      </c>
+      <c r="H1558" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1558" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1558" t="n">
+        <v>400000</v>
+      </c>
+      <c r="L1558" t="inlineStr">
+        <is>
+          <t>VivaReal | id:2889526287</t>
+        </is>
+      </c>
+      <c r="M1558" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="N1558" t="inlineStr"/>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1559" t="inlineStr">
+        <is>
+          <t>vivareal.com.br</t>
+        </is>
+      </c>
+      <c r="C1559" t="inlineStr">
+        <is>
+          <t>VivaReal</t>
+        </is>
+      </c>
+      <c r="D1559" t="inlineStr"/>
+      <c r="E1559" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="F1559" t="inlineStr">
+        <is>
+          <t>Zona 07 · Rua Rui Barbosa</t>
+        </is>
+      </c>
+      <c r="G1559" t="n">
+        <v>70</v>
+      </c>
+      <c r="H1559" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1559" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1559" t="n">
+        <v>420000</v>
+      </c>
+      <c r="L1559" t="inlineStr">
+        <is>
+          <t>VivaReal | id:2802293515</t>
+        </is>
+      </c>
+      <c r="M1559" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="N1559" t="inlineStr"/>
+    </row>
+    <row r="1560">
+      <c r="A1560" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1560" t="inlineStr">
+        <is>
+          <t>vivareal.com.br</t>
+        </is>
+      </c>
+      <c r="C1560" t="inlineStr">
+        <is>
+          <t>VivaReal</t>
+        </is>
+      </c>
+      <c r="D1560" t="inlineStr"/>
+      <c r="E1560" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="F1560" t="inlineStr">
+        <is>
+          <t>Jardim Oriental · Rua Ivonete Aparecida Ribeiro Matos</t>
+        </is>
+      </c>
+      <c r="G1560" t="n">
+        <v>140</v>
+      </c>
+      <c r="H1560" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1560" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1560" t="n">
+        <v>650000</v>
+      </c>
+      <c r="L1560" t="inlineStr">
+        <is>
+          <t>VivaReal | id:2877323215</t>
+        </is>
+      </c>
+      <c r="M1560" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="N1560" t="inlineStr"/>
+    </row>
+    <row r="1561">
+      <c r="A1561" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1561" t="inlineStr">
+        <is>
+          <t>vivareal.com.br</t>
+        </is>
+      </c>
+      <c r="C1561" t="inlineStr">
+        <is>
+          <t>VivaReal</t>
+        </is>
+      </c>
+      <c r="D1561" t="inlineStr"/>
+      <c r="E1561" t="inlineStr">
+        <is>
+          <t>Terreno</t>
+        </is>
+      </c>
+      <c r="F1561" t="inlineStr">
+        <is>
+          <t>Jardim Oriental · Rua Pioneira Idalina Caliman Mariani</t>
+        </is>
+      </c>
+      <c r="G1561" t="n">
+        <v>200</v>
+      </c>
+      <c r="K1561" t="n">
+        <v>210000</v>
+      </c>
+      <c r="L1561" t="inlineStr">
+        <is>
+          <t>VivaReal | id:2870611330</t>
+        </is>
+      </c>
+      <c r="M1561" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="N1561" t="inlineStr"/>
+    </row>
+    <row r="1562">
+      <c r="A1562" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1562" t="inlineStr">
+        <is>
+          <t>vivareal.com.br</t>
+        </is>
+      </c>
+      <c r="C1562" t="inlineStr">
+        <is>
+          <t>VivaReal</t>
+        </is>
+      </c>
+      <c r="D1562" t="inlineStr"/>
+      <c r="E1562" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="F1562" t="inlineStr">
+        <is>
+          <t>Conjunto Habitacional Requião · Rua Antônio Alves Munhoz</t>
+        </is>
+      </c>
+      <c r="G1562" t="n">
+        <v>150</v>
+      </c>
+      <c r="H1562" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1562" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1562" t="n">
+        <v>400000</v>
+      </c>
+      <c r="L1562" t="inlineStr">
+        <is>
+          <t>VivaReal | id:2852429173</t>
+        </is>
+      </c>
+      <c r="M1562" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="N1562" t="inlineStr"/>
+    </row>
+    <row r="1563">
+      <c r="A1563" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1563" t="inlineStr">
+        <is>
+          <t>vivareal.com.br</t>
+        </is>
+      </c>
+      <c r="C1563" t="inlineStr">
+        <is>
+          <t>VivaReal</t>
+        </is>
+      </c>
+      <c r="D1563" t="inlineStr"/>
+      <c r="E1563" t="inlineStr">
+        <is>
+          <t>Terreno</t>
+        </is>
+      </c>
+      <c r="F1563" t="inlineStr">
+        <is>
+          <t>Parque Tarumã · Rua Pioneiro João Custódio Pereira</t>
+        </is>
+      </c>
+      <c r="G1563" t="n">
+        <v>368</v>
+      </c>
+      <c r="K1563" t="n">
+        <v>360000</v>
+      </c>
+      <c r="L1563" t="inlineStr">
+        <is>
+          <t>VivaReal | id:2765141236</t>
+        </is>
+      </c>
+      <c r="M1563" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="N1563" t="inlineStr"/>
+    </row>
+    <row r="1564">
+      <c r="A1564" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1564" t="inlineStr">
+        <is>
+          <t>vivareal.com.br</t>
+        </is>
+      </c>
+      <c r="C1564" t="inlineStr">
+        <is>
+          <t>VivaReal</t>
+        </is>
+      </c>
+      <c r="D1564" t="inlineStr"/>
+      <c r="E1564" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="F1564" t="inlineStr">
+        <is>
+          <t>Loteamento Sumaré · Rua Pioneiro Genir Galli</t>
+        </is>
+      </c>
+      <c r="G1564" t="n">
+        <v>58</v>
+      </c>
+      <c r="H1564" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1564" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1564" t="n">
+        <v>280000</v>
+      </c>
+      <c r="L1564" t="inlineStr">
+        <is>
+          <t>VivaReal | id:2888858307</t>
+        </is>
+      </c>
+      <c r="M1564" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="N1564" t="inlineStr"/>
+    </row>
+    <row r="1565">
+      <c r="A1565" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1565" t="inlineStr">
+        <is>
+          <t>vivareal.com.br</t>
+        </is>
+      </c>
+      <c r="C1565" t="inlineStr">
+        <is>
+          <t>VivaReal</t>
+        </is>
+      </c>
+      <c r="D1565" t="inlineStr"/>
+      <c r="E1565" t="inlineStr">
+        <is>
+          <t>Sobrado</t>
+        </is>
+      </c>
+      <c r="F1565" t="inlineStr">
+        <is>
+          <t>Copacabana Residencial · Rua Pioneiro Basílio José da Silva</t>
+        </is>
+      </c>
+      <c r="G1565" t="n">
+        <v>180</v>
+      </c>
+      <c r="H1565" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1565" t="n">
+        <v>350000</v>
+      </c>
+      <c r="L1565" t="inlineStr">
+        <is>
+          <t>VivaReal | id:2895401806</t>
+        </is>
+      </c>
+      <c r="M1565" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="N1565" t="inlineStr"/>
+    </row>
+    <row r="1566">
+      <c r="A1566" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1566" t="inlineStr">
+        <is>
+          <t>vivareal.com.br</t>
+        </is>
+      </c>
+      <c r="C1566" t="inlineStr">
+        <is>
+          <t>VivaReal</t>
+        </is>
+      </c>
+      <c r="D1566" t="inlineStr"/>
+      <c r="E1566" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="F1566" t="inlineStr">
+        <is>
+          <t>Jardim América · Avenida das Indústrias</t>
+        </is>
+      </c>
+      <c r="G1566" t="n">
+        <v>46</v>
+      </c>
+      <c r="H1566" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1566" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1566" t="n">
+        <v>280000</v>
+      </c>
+      <c r="L1566" t="inlineStr">
+        <is>
+          <t>VivaReal | id:2890750498</t>
+        </is>
+      </c>
+      <c r="M1566" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="N1566" t="inlineStr"/>
+    </row>
+    <row r="1567">
+      <c r="A1567" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1567" t="inlineStr">
+        <is>
+          <t>vivareal.com.br</t>
+        </is>
+      </c>
+      <c r="C1567" t="inlineStr">
+        <is>
+          <t>VivaReal</t>
+        </is>
+      </c>
+      <c r="D1567" t="inlineStr"/>
+      <c r="E1567" t="inlineStr">
+        <is>
+          <t>Terreno</t>
+        </is>
+      </c>
+      <c r="F1567" t="inlineStr">
+        <is>
+          <t>Jardim Novo Paulista · Rua Pioneira Nair Bueno da Fonseca</t>
+        </is>
+      </c>
+      <c r="G1567" t="n">
+        <v>200</v>
+      </c>
+      <c r="K1567" t="n">
+        <v>130000</v>
+      </c>
+      <c r="L1567" t="inlineStr">
+        <is>
+          <t>VivaReal | id:2895401807</t>
+        </is>
+      </c>
+      <c r="M1567" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="N1567" t="inlineStr"/>
+    </row>
+    <row r="1568">
+      <c r="A1568" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1568" t="inlineStr">
+        <is>
+          <t>vivareal.com.br</t>
+        </is>
+      </c>
+      <c r="C1568" t="inlineStr">
+        <is>
+          <t>VivaReal</t>
+        </is>
+      </c>
+      <c r="D1568" t="inlineStr"/>
+      <c r="E1568" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="F1568" t="inlineStr">
+        <is>
+          <t>Jardim Monte Rei · Rua Aurélio Quáglia</t>
+        </is>
+      </c>
+      <c r="G1568" t="n">
+        <v>115</v>
+      </c>
+      <c r="H1568" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1568" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1568" t="n">
+        <v>490000</v>
+      </c>
+      <c r="L1568" t="inlineStr">
+        <is>
+          <t>VivaReal | id:2760543324</t>
+        </is>
+      </c>
+      <c r="M1568" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="N1568" t="inlineStr"/>
+    </row>
+    <row r="1569">
+      <c r="A1569" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1569" t="inlineStr">
+        <is>
+          <t>vivareal.com.br</t>
+        </is>
+      </c>
+      <c r="C1569" t="inlineStr">
+        <is>
+          <t>VivaReal</t>
+        </is>
+      </c>
+      <c r="D1569" t="inlineStr"/>
+      <c r="E1569" t="inlineStr">
+        <is>
+          <t>Terreno</t>
+        </is>
+      </c>
+      <c r="F1569" t="inlineStr">
+        <is>
+          <t>Vila Morangueira · Rua La Paz</t>
+        </is>
+      </c>
+      <c r="G1569" t="n">
+        <v>480</v>
+      </c>
+      <c r="K1569" t="n">
+        <v>550000</v>
+      </c>
+      <c r="L1569" t="inlineStr">
+        <is>
+          <t>VivaReal | id:2825361426</t>
+        </is>
+      </c>
+      <c r="M1569" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="N1569" t="inlineStr"/>
+    </row>
+    <row r="1570">
+      <c r="A1570" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1570" t="inlineStr">
+        <is>
+          <t>vivareal.com.br</t>
+        </is>
+      </c>
+      <c r="C1570" t="inlineStr">
+        <is>
+          <t>VivaReal</t>
+        </is>
+      </c>
+      <c r="D1570" t="inlineStr"/>
+      <c r="E1570" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="F1570" t="inlineStr">
+        <is>
+          <t>Jardim Rebouças · Rua Pioneiro Salvador Kessa</t>
+        </is>
+      </c>
+      <c r="G1570" t="n">
+        <v>165</v>
+      </c>
+      <c r="H1570" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1570" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1570" t="n">
+        <v>350000</v>
+      </c>
+      <c r="L1570" t="inlineStr">
+        <is>
+          <t>VivaReal | id:2895391591</t>
+        </is>
+      </c>
+      <c r="M1570" t="inlineStr">
+        <is>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="N1570" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N1"/>
@@ -59720,7 +59945,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-06-28 14:42</t>
+          <t>2026-07-01 08:42</t>
         </is>
       </c>
     </row>
@@ -59735,6 +59960,11 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-07-01 08:42</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>Grupo de busca de imóveis Maringá</t>
@@ -59752,6 +59982,11 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-07-01 08:42</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>Grupo imóveis Maringá</t>
@@ -59769,6 +60004,11 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-07-01 08:42</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Grupo de angariações</t>
@@ -59786,6 +60026,11 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-07-01 08:42</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>Grupo corretores Maringá</t>
@@ -59803,6 +60048,11 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-07-01 08:42</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Grupo casas Maringá</t>
@@ -59820,6 +60070,11 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-07-01 08:42</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>Corretores parceiros Maringá</t>
@@ -59837,6 +60092,11 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-07-01 08:42</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>Grupo imóveis casas Maringá</t>
@@ -59854,6 +60114,11 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-07-01 08:42</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>Casas novas Maringá</t>
@@ -59871,6 +60136,11 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-07-01 08:42</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>Grupo INNOVARE corretores</t>
@@ -59888,6 +60158,11 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-07-01 08:42</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>Grupo parceiros Prontos Patrimônio</t>
@@ -59905,6 +60180,11 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-07-01 08:42</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>Grupo corretores Maringá</t>
@@ -59922,6 +60202,11 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-07-01 08:42</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>Grupo Negócio Fechado Maringá</t>
@@ -59939,6 +60224,11 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-07-01 08:42</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>Parceiros Majestic corretores</t>
@@ -59956,6 +60246,11 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-07-01 08:42</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>Grupo universo dos imóveis</t>
@@ -59971,6 +60266,11 @@
       <c r="B17" t="inlineStr">
         <is>
           <t>Sim</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-07-01 08:42</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
